--- a/Assets/Planning/QA/Revenger_BTL.xlsx
+++ b/Assets/Planning/QA/Revenger_BTL.xlsx
@@ -16,21 +16,27 @@
     <sheet name="5" sheetId="6" r:id="rId9"/>
     <sheet name="6" sheetId="7" r:id="rId10"/>
     <sheet name="7" sheetId="8" r:id="rId11"/>
+    <sheet name="8" sheetId="9" r:id="rId12"/>
+    <sheet name="9-1" sheetId="10" r:id="rId13"/>
+    <sheet name="9-2" sheetId="11" r:id="rId14"/>
+    <sheet name="10-1" sheetId="12" r:id="rId15"/>
+    <sheet name="10-2" sheetId="13" r:id="rId16"/>
+    <sheet name="11" sheetId="14" r:id="rId17"/>
   </sheets>
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1760254016" val="1228" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1760254016" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1760254016" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1760254016"/>
+      <pm:revision xmlns:pm="smNativeData" day="1760967717" val="1228" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1760967717" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1760967717" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1760967717"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -57,6 +63,18 @@
   </si>
   <si>
     <t>Charger</t>
+  </si>
+  <si>
+    <t>9 - 1</t>
+  </si>
+  <si>
+    <t>9 - 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 -1 </t>
+  </si>
+  <si>
+    <t>10 -2</t>
   </si>
   <si>
     <t>Product</t>
@@ -258,12 +276,84 @@
   <si>
     <t>인벤토리 UI의 우선순위를 수정해 일시정지화면 Ui를 우선적으로 둬야야 해결될 것으로 보임.</t>
   </si>
+  <si>
+    <t>9c886e3 - 8</t>
+  </si>
+  <si>
+    <t>메인매뉴를 통해 Home 진입시 라이팅 버그</t>
+  </si>
+  <si>
+    <t>메인메뉴 Scene을 통해 게임을 시작하면서 Home에 진입시 방의 라이팅이 없어지는 버그 발생</t>
+  </si>
+  <si>
+    <t>Home에 라이팅을 제대로 추가, 적용하지 않은 문제로 판단</t>
+  </si>
+  <si>
+    <t>9c886e3 - 9  - 1</t>
+  </si>
+  <si>
+    <t>세탁소 밸브 퍼즐 디자인 미완성</t>
+  </si>
+  <si>
+    <t>세탁소 퍼즐의 밸브 오브젝트의 머테리얼 누락, 미완성</t>
+  </si>
+  <si>
+    <t>아직 퍼즐의 디자인이 미완성인것으로 판단</t>
+  </si>
+  <si>
+    <t>9c886e3 - 9  - 2</t>
+  </si>
+  <si>
+    <t>세탁소 문 벽 콜리전 문제</t>
+  </si>
+  <si>
+    <t>세탁소 퍼즐 구간의 문에 플레이어가 질주하면서 문의 끝으로 돌진할 경우 일정 확률로 문을 뚫고 나가게 됨</t>
+  </si>
+  <si>
+    <t>벽의 물리판정과 플레이어가 달릴때 벽에 간섭을 덜 받을 수 있게 수정하면 해결이 가능할 것 같음</t>
+  </si>
+  <si>
+    <t>9c886e3 - 10 - 1</t>
+  </si>
+  <si>
+    <t>식당 오브젝트 물리판정 누락</t>
+  </si>
+  <si>
+    <t>식당의 책상 오브젝트의 물리판정이 없어 플레이어가 통과함</t>
+  </si>
+  <si>
+    <t>아직 팩상의 물리판정을 넣지 않은 것으로 판단</t>
+  </si>
+  <si>
+    <t>9c886e3 - 10 - 2</t>
+  </si>
+  <si>
+    <t>식당 천장 라이트 효과 누수</t>
+  </si>
+  <si>
+    <t>식당 옥상에 촛볼관련 라이트가 바로 윗층에 있는 화로 불 라이팅이 뚫려 보이는 현상이 보임</t>
+  </si>
+  <si>
+    <t>해당 화로의 라이트 효과를 직접 수정하면 해결될 것으로 보임</t>
+  </si>
+  <si>
+    <t>9c886e3 - 11</t>
+  </si>
+  <si>
+    <t>서재실 벽문제</t>
+  </si>
+  <si>
+    <t>서재실에 있는 책장 오브젝트에 플레이어가 달리기를 하며 돌진하면 가끔 벽을 뚫어 맵 밖으로 떨어지는 문제가 발생</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해당 책장의 콜리전 판정을 좀 넓으면서 널널히 줘야 해결될 것으로 보임 </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="5" formatCode="#,##0\ &quot;₩&quot;;\-#,##0\ &quot;₩&quot;"/>
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;₩&quot;;[Red]\-#,##0\ &quot;₩&quot;"/>
     <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;₩&quot;;\-#,##0.00\ &quot;₩&quot;"/>
@@ -274,8 +364,9 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₩_-;\-* #,##0.00\ _₩_-;_-* &quot;-&quot;??\ _₩_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="YY&quot;-&quot;M&quot;-&quot;D\ h:mm;@"/>
     <numFmt numFmtId="14" formatCode="M/D/YYYY"/>
+    <numFmt numFmtId="165" formatCode="MM/DD"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="23">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -284,7 +375,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -299,7 +390,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -315,7 +406,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="180" lang="default"/>
             <pm:cs face="Times New Roman" sz="180" lang="default"/>
             <pm:ea face="SimSun" sz="180" lang="default"/>
@@ -332,7 +423,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -347,7 +438,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default"/>
             <pm:cs face="Times New Roman" sz="180" lang="default"/>
             <pm:ea face="SimSun" sz="180" lang="default"/>
@@ -363,7 +454,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
@@ -379,7 +470,7 @@
       <sz val="12"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="240" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="240" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="240" lang="default" weight="bold"/>
@@ -396,7 +487,7 @@
       <sz val="6"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="120" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="120" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="120" lang="default" weight="bold"/>
@@ -412,7 +503,7 @@
       <sz val="6"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="120" lang="default"/>
             <pm:cs face="Times New Roman" sz="120" lang="default"/>
             <pm:ea face="SimSun" sz="120" lang="default"/>
@@ -428,7 +519,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
@@ -443,7 +534,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default"/>
             <pm:cs face="Times New Roman" sz="160" lang="default"/>
             <pm:ea face="SimSun" sz="160" lang="default"/>
@@ -460,7 +551,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -478,7 +569,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -496,7 +587,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -514,7 +605,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -532,7 +623,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -550,7 +641,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -568,11 +659,101 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1760254016" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
             <hyperlink type="5" url="" location="'7'!A1" text=""/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
+            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
+            <pm:cs face="맑은 고딕" sz="220" lang="default"/>
+            <pm:ea face="맑은 고딕" sz="220" lang="default"/>
+            <hyperlink type="5" url="" location="'9-1'!A1" text=""/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
+            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
+            <pm:cs face="맑은 고딕" sz="220" lang="default"/>
+            <pm:ea face="맑은 고딕" sz="220" lang="default"/>
+            <hyperlink type="5" url="" location="'9-2'!A1" text=""/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
+            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
+            <pm:cs face="맑은 고딕" sz="220" lang="default"/>
+            <pm:ea face="맑은 고딕" sz="220" lang="default"/>
+            <hyperlink type="5" url="" location="'10-1'!A1" text=""/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
+            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
+            <pm:cs face="맑은 고딕" sz="220" lang="default"/>
+            <pm:ea face="맑은 고딕" sz="220" lang="default"/>
+            <hyperlink type="5" url="" location="'10-2'!A1" text=""/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1760967717" fgClr="0000FF" ulstyle="single" kern="1">
+            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
+            <pm:cs face="맑은 고딕" sz="220" lang="default"/>
+            <pm:ea face="맑은 고딕" sz="220" lang="default"/>
+            <hyperlink type="5" url="" location="'11'!A1" text=""/>
           </pm:charSpec>
         </ext>
       </extLst>
@@ -591,7 +772,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1760254016" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1760967717" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -605,7 +786,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1760254016" type="1" fgLvl="100" fgClr="00D8D8D8" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1760967717" type="1" fgLvl="100" fgClr="00D8D8D8" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -616,7 +797,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1760254016" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1760967717" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -654,7 +835,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1760254016" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1760967717" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -676,7 +857,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016"/>
+          <pm:border xmlns:pm="smNativeData" id="1760967717"/>
         </ext>
       </extLst>
     </border>
@@ -695,7 +876,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016"/>
+          <pm:border xmlns:pm="smNativeData" id="1760967717"/>
         </ext>
       </extLst>
     </border>
@@ -714,7 +895,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016">
+          <pm:border xmlns:pm="smNativeData" id="1760967717">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -738,7 +919,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016">
+          <pm:border xmlns:pm="smNativeData" id="1760967717">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -762,7 +943,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016">
+          <pm:border xmlns:pm="smNativeData" id="1760967717">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -786,7 +967,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016">
+          <pm:border xmlns:pm="smNativeData" id="1760967717">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
         </ext>
@@ -807,7 +988,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016">
+          <pm:border xmlns:pm="smNativeData" id="1760967717">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -829,7 +1010,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016">
+          <pm:border xmlns:pm="smNativeData" id="1760967717">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
         </ext>
@@ -850,7 +1031,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016">
+          <pm:border xmlns:pm="smNativeData" id="1760967717">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -872,7 +1053,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016">
+          <pm:border xmlns:pm="smNativeData" id="1760967717">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -894,7 +1075,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016">
+          <pm:border xmlns:pm="smNativeData" id="1760967717">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -916,7 +1097,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016">
+          <pm:border xmlns:pm="smNativeData" id="1760967717">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -939,7 +1120,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016">
+          <pm:border xmlns:pm="smNativeData" id="1760967717">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -961,7 +1142,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016">
+          <pm:border xmlns:pm="smNativeData" id="1760967717">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -984,7 +1165,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1760254016"/>
+          <pm:border xmlns:pm="smNativeData" id="1760967717"/>
         </ext>
       </extLst>
     </border>
@@ -997,7 +1178,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1112,6 +1293,21 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -1120,10 +1316,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1760254016" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1760967717" count="1">
         <pm:charStyle name="보통" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1760254016" count="2">
+      <pm:colors xmlns:pm="smNativeData" id="1760967717" count="2">
         <pm:color name="색: 24" rgb="D8D8D8"/>
         <pm:color name="색: 25" rgb="BFBFBF"/>
       </pm:colors>
@@ -1154,7 +1350,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_QFjraBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAMwCAAAfAAAACQAAABAB4wMAAAAA8SEAAHIpAADrDwAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_JTz2aBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAMwCAAAfAAAACQAAABAB4wMAAAAA8SEAAHIpAADrDwAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1169,6 +1365,169 @@
         <a:xfrm>
           <a:off x="0" y="5517515"/>
           <a:ext cx="6737350" cy="2587625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>254000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>673735</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>100330</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="smNativeData">
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_JTz2aBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAUAAAAAAAAAMEDAAAjAAAACQAAAHwB/QMAAAAArSAAAI0pAAAEGAAAAAAAAA=="/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5311775"/>
+          <a:ext cx="6754495" cy="3903980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>10160</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>33655</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>263525</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="smNativeData">
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_JTz2aBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAB3AQAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAH8ADwAhAAAACQAAAEkDjwEQAAAA/CAAAPcmAAAhFQAAAAAAAA=="/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10160" y="5361940"/>
+          <a:ext cx="6334125" cy="3434715"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>204470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>437515</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>260985</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="smNativeData">
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_JTz2aBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAhAAAAAAAAAAUDAAAtAAAACAAAANsDlwIAAAAAATYAAPEjAABRFAAAAAAAAA=="/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="8778875"/>
+          <a:ext cx="5842635" cy="3302635"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1210,7 +1569,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_QFjraBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAgtKYBHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAGYBDwAiAAAACQAAAHgCVAMQAAAAXCEAAM0oAAAUFgAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_JTz2aBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAgtKYBHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAGYBDwAiAAAACQAAAHgCVAMQAAAAXCEAAM0oAAAUFgAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1266,7 +1625,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_QFjraBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAgtKYBHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAEgAAQAeAAAACQAAAF8D5AMBAAAA5SAAAHIpAABDEAAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_JTz2aBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAgtKYBHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAEgAAQAeAAAACQAAAF8D5AMBAAAA5SAAAHIpAABDEAAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1322,7 +1681,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_QFjraBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAF8AAAAiAAAACQAAAK0DxgMAAAAA7yAAAFQpAAABFwAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_JTz2aBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAGAAAAAiAAAACQAAAKwDxgMAAAAA7yAAAFQpAAABFwAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1378,7 +1737,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_QFjraBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAMEAOwAjAAAACQAAAN4B8wM9AAAAFyEAAEUpAADDFwAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_JTz2aBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAMAAOwAjAAAACQAAAN4B8wM9AAAAFyEAAEUpAADDFwAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1393,6 +1752,229 @@
         <a:xfrm>
           <a:off x="38735" y="5379085"/>
           <a:ext cx="6708775" cy="3862705"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1905</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>631190</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="smNativeData">
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_JTz2aBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAABAQD/HgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAAcAAAAjAAAACQAAACUCvQMAAAAAyiAAAEopAAAtGAAAAAAAAA=="/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5330190"/>
+          <a:ext cx="6711950" cy="3930015"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>668655</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>67945</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="smNativeData">
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_JTz2aBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAJ4AAAAjAAAACQAAAAAB9QMAAAAACSEAAIUpAAB1FwAAAAAAAA=="/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5370195"/>
+          <a:ext cx="6749415" cy="3813175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>260985</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>135255</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림1"/>
+        <xdr:cNvPicPr>
+          <a:extLst>
+            <a:ext uri="smNativeData">
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_JTz2aBMAAAAlAAAAEQAAAI8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAUAAAAAAAAANsDAQAjAAAACQAAAAAC1gMBAAAAuCAAAGMpAAAwGAAAAAAAAA=="/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635" y="5318760"/>
+          <a:ext cx="6727825" cy="3931920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>17780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>673735</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>106045</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="smNativeData">
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_JTz2aBMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAADkAQAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAEQAAAAjAAAACQAAAJIB/QMAAAAA4yAAAI0pAADXFwAAAAAAAA=="/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5346065"/>
+          <a:ext cx="6754495" cy="3875405"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1686,7 +2268,7 @@
       </c>
       <c r="G1" s="14">
         <f aca="1">TODAY()</f>
-        <v>45942</v>
+        <v>45950</v>
       </c>
       <c r="H1" s="14"/>
     </row>
@@ -1901,7 +2483,8 @@
         <f>'6'!C4</f>
         <v>45942</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="8">
+        <f>'6'!C3</f>
         <v>6</v>
       </c>
       <c r="D9" s="8" t="str">
@@ -1933,7 +2516,8 @@
         <f>'7'!C4</f>
         <v>45942</v>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="8">
+        <f>'7'!C3</f>
         <v>7</v>
       </c>
       <c r="D10" s="8" t="str">
@@ -1958,64 +2542,202 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="A11" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9">
+        <f>'8'!C4</f>
+        <v>45950</v>
+      </c>
+      <c r="C11" s="8" t="str">
+        <f>'8'!C3</f>
+        <v>9c886e3 - 8</v>
+      </c>
+      <c r="D11" s="9" t="str">
+        <f>'8'!C9</f>
+        <v>Design</v>
+      </c>
+      <c r="E11" s="8" t="str">
+        <f>'8'!C5</f>
+        <v>High</v>
+      </c>
+      <c r="F11" s="12" t="str">
+        <f>'8'!C12</f>
+        <v>메인매뉴를 통해 Home 진입시 라이팅 버그</v>
+      </c>
+      <c r="G11" s="8" t="str">
+        <f>'7'!H4</f>
+        <v>김사윤</v>
+      </c>
+      <c r="H11" s="9" t="str">
+        <f>'8'!H9</f>
+        <v>엄기영</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="A12" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="9">
+        <f>'9-1'!C4</f>
+        <v>45950</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <f>'9-1'!C3</f>
+        <v>9c886e3 - 9  - 1</v>
+      </c>
+      <c r="D12" s="8" t="str">
+        <f>'9-1'!C9</f>
+        <v>Design</v>
+      </c>
+      <c r="E12" s="8" t="str">
+        <f>'9-1'!C5</f>
+        <v>Mid</v>
+      </c>
+      <c r="F12" s="12" t="str">
+        <f>'9-1'!C12</f>
+        <v>세탁소 밸브 퍼즐 디자인 미완성</v>
+      </c>
+      <c r="G12" s="8" t="str">
+        <f>'7'!H4</f>
+        <v>김사윤</v>
+      </c>
+      <c r="H12" s="8" t="str">
+        <f>'9-1'!H9</f>
+        <v>엄기영</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="A13" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="9">
+        <f>'9-2'!C4</f>
+        <v>45950</v>
+      </c>
+      <c r="C13" s="8" t="str">
+        <f>'9-2'!C3</f>
+        <v>9c886e3 - 9  - 2</v>
+      </c>
+      <c r="D13" s="8" t="str">
+        <f>'9-2'!C9</f>
+        <v>Design</v>
+      </c>
+      <c r="E13" s="8" t="str">
+        <f>'9-2'!C5</f>
+        <v>Mid</v>
+      </c>
+      <c r="F13" s="12" t="str">
+        <f>'9-2'!C12</f>
+        <v>세탁소 문 벽 콜리전 문제</v>
+      </c>
+      <c r="G13" s="8" t="str">
+        <f>'7'!H4</f>
+        <v>김사윤</v>
+      </c>
+      <c r="H13" s="8" t="str">
+        <f>'9-2'!H9</f>
+        <v>엄기영</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
+      <c r="A14" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="9">
+        <f>'10-1'!C4</f>
+        <v>45950</v>
+      </c>
+      <c r="C14" s="8" t="str">
+        <f>'10-1'!C3</f>
+        <v>9c886e3 - 10 - 1</v>
+      </c>
+      <c r="D14" s="8" t="str">
+        <f>'10-1'!C9</f>
+        <v>Design</v>
+      </c>
+      <c r="E14" s="8" t="str">
+        <f>'10-2'!C5</f>
+        <v>Low</v>
+      </c>
+      <c r="F14" s="12" t="str">
+        <f>'10-1'!C12</f>
+        <v>식당 오브젝트 물리판정 누락</v>
+      </c>
+      <c r="G14" s="8" t="str">
+        <f>'7'!H4</f>
+        <v>김사윤</v>
+      </c>
+      <c r="H14" s="8" t="str">
+        <f>'10-1'!H9</f>
+        <v>엄기영</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="A15" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="9">
+        <f>'10-2'!C4</f>
+        <v>45950</v>
+      </c>
+      <c r="C15" s="8" t="str">
+        <f>'10-2'!C3</f>
+        <v>9c886e3 - 10 - 2</v>
+      </c>
+      <c r="D15" s="8" t="str">
+        <f>'10-2'!C9</f>
+        <v>Design</v>
+      </c>
+      <c r="E15" s="8" t="str">
+        <f>'10-2'!C5</f>
+        <v>Low</v>
+      </c>
+      <c r="F15" s="12" t="str">
+        <f>'10-2'!C12</f>
+        <v>식당 천장 라이트 효과 누수</v>
+      </c>
+      <c r="G15" s="8" t="str">
+        <f>'7'!H4</f>
+        <v>김사윤</v>
+      </c>
+      <c r="H15" s="8" t="str">
+        <f>'10-2'!H9</f>
+        <v>엄기영</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
+      <c r="A16" s="42" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="9">
+        <f>'11'!C4</f>
+        <v>45950</v>
+      </c>
+      <c r="C16" s="8" t="str">
+        <f>'11'!C3</f>
+        <v>9c886e3 - 11</v>
+      </c>
+      <c r="D16" s="8" t="str">
+        <f>'11'!C9</f>
+        <v>Design</v>
+      </c>
+      <c r="E16" s="8" t="str">
+        <f>'11'!C5</f>
+        <v>Mid</v>
+      </c>
+      <c r="F16" s="12" t="str">
+        <f>'11'!C12</f>
+        <v>서재실 벽문제</v>
+      </c>
+      <c r="G16" s="8" t="str">
+        <f>'7'!H4</f>
+        <v>김사윤</v>
+      </c>
+      <c r="H16" s="8" t="str">
+        <f>'11'!H9</f>
+        <v>엄기영</v>
+      </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="8"/>
@@ -2170,11 +2892,17 @@
     <hyperlink ref="A8" location="'5'!A1"/>
     <hyperlink ref="A9" location="'6'!A1"/>
     <hyperlink ref="A10" location="'7'!A1"/>
+    <hyperlink ref="A11" location="'1'!A1"/>
+    <hyperlink ref="A12" location="'9-1'!A1"/>
+    <hyperlink ref="A13" location="'9-2'!A1"/>
+    <hyperlink ref="A14" location="'10-1'!A1"/>
+    <hyperlink ref="A15" location="'10-2'!A1"/>
+    <hyperlink ref="A16" location="'11'!A1"/>
   </hyperlinks>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1760254016" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2183,16 +2911,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760254016" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -2201,7 +2929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="21"/>
@@ -2212,37 +2940,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I1" s="25" t="n">
-        <v>45938.7034722222234</v>
+        <v>45950.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -2254,28 +2982,28 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="8" t="n">
-        <v>1</v>
+      <c r="C3" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -2285,47 +3013,47 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45920</v>
+        <v>45950</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2334,27 +3062,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -2368,40 +3096,40 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -2409,7 +3137,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2423,11 +3151,11 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="22" t="s">
-        <v>47</v>
+      <c r="C12" s="31" t="s">
+        <v>84</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -2438,8 +3166,8 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="15" t="s">
-        <v>48</v>
+      <c r="A13" s="32" t="s">
+        <v>85</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -2465,7 +3193,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -2503,7 +3231,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -2517,7 +3245,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -2543,7 +3271,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -2912,7 +3640,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1760254016" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2921,17 +3649,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760254016" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -2940,7 +3668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="21"/>
@@ -2951,37 +3679,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I1" s="25" t="n">
-        <v>45938.7034722222234</v>
+        <v>45950.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -2993,28 +3721,28 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="8" t="n">
-        <v>2</v>
+      <c r="C3" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -3024,47 +3752,47 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45920</v>
+        <v>45950</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3073,27 +3801,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -3107,40 +3835,40 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -3148,7 +3876,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3162,11 +3890,11 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="22" t="s">
-        <v>54</v>
+      <c r="C12" s="31" t="s">
+        <v>88</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -3177,8 +3905,8 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="15" t="s">
-        <v>55</v>
+      <c r="A13" s="32" t="s">
+        <v>89</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -3204,7 +3932,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -3242,7 +3970,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -3256,7 +3984,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -3282,7 +4010,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -3651,7 +4379,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1760254016" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -3660,17 +4388,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760254016" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -3679,7 +4407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="21"/>
@@ -3690,37 +4418,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I1" s="25" t="n">
-        <v>45938.7034722222234</v>
+        <v>45950.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3732,28 +4460,28 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="8" t="n">
-        <v>3</v>
+      <c r="C3" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -3763,47 +4491,47 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45920</v>
+        <v>45950</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3812,27 +4540,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -3846,40 +4574,40 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -3887,7 +4615,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3901,11 +4629,11 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="22" t="s">
-        <v>60</v>
+      <c r="C12" s="31" t="s">
+        <v>92</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -3916,8 +4644,8 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="15" t="s">
-        <v>61</v>
+      <c r="A13" s="32" t="s">
+        <v>93</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -3943,7 +4671,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -3981,7 +4709,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -3995,7 +4723,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -4021,7 +4749,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -4390,7 +5118,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1760254016" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -4399,16 +5127,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760254016" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -4417,7 +5146,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="21"/>
@@ -4428,37 +5157,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I1" s="25" t="n">
-        <v>45938.7034722222234</v>
+        <v>45950.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -4470,28 +5199,28 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="8" t="n">
-        <v>4</v>
+      <c r="C3" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -4501,47 +5230,47 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45927</v>
+        <v>45950</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4550,27 +5279,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4584,40 +5313,40 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -4625,7 +5354,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4639,11 +5368,11 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="31" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -4655,7 +5384,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="32" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -4681,7 +5410,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -4719,7 +5448,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -4733,7 +5462,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -4759,7 +5488,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -5128,7 +5857,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1760254016" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -5137,16 +5866,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760254016" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -5155,7 +5885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="21"/>
@@ -5166,37 +5896,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I1" s="25" t="n">
-        <v>45938.7034722222234</v>
+        <v>45950.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -5208,28 +5938,28 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="8" t="n">
-        <v>5</v>
+      <c r="C3" s="8" t="s">
+        <v>99</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -5239,47 +5969,47 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45927</v>
+        <v>45950</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -5288,27 +6018,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -5322,40 +6052,40 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -5363,7 +6093,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -5377,11 +6107,11 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="31" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -5393,7 +6123,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="32" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -5419,7 +6149,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -5457,7 +6187,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -5471,7 +6201,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -5497,7 +6227,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -5866,7 +6596,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1760254016" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -5875,17 +6605,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760254016" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -5894,7 +6624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="21"/>
@@ -5905,37 +6635,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I1" s="25" t="n">
-        <v>45942.6756944444423</v>
+        <v>45938.7034722222234</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -5947,28 +6677,28 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -5978,47 +6708,47 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45942</v>
+        <v>45920</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -6027,27 +6757,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -6061,40 +6791,40 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -6102,7 +6832,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6116,11 +6846,11 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="31" t="s">
-        <v>69</v>
+      <c r="C12" s="22" t="s">
+        <v>51</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -6131,8 +6861,8 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="32" t="s">
-        <v>70</v>
+      <c r="A13" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -6158,7 +6888,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -6196,7 +6926,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -6210,7 +6940,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -6236,7 +6966,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -6605,7 +7335,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1760254016" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -6614,17 +7344,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760254016" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -6633,7 +7363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="21"/>
@@ -6644,37 +7374,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I1" s="25" t="n">
-        <v>45942.6756944444423</v>
+        <v>45938.7034722222234</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -6686,28 +7416,28 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -6717,47 +7447,47 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45942</v>
+        <v>45920</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -6766,27 +7496,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -6800,40 +7530,40 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -6841,7 +7571,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6855,11 +7585,11 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="31" t="s">
-        <v>72</v>
+      <c r="C12" s="22" t="s">
+        <v>58</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -6870,8 +7600,8 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="32" t="s">
-        <v>73</v>
+      <c r="A13" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -6897,7 +7627,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -6935,7 +7665,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -6949,7 +7679,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -6975,7 +7705,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -7344,7 +8074,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1760254016" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -7353,17 +8083,4449 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1760254016" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1760254016" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760254016" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:S46"/>
+  <sheetFormatPr defaultRowHeight="21"/>
+  <cols>
+    <col min="1" max="10" width="8.793388" customWidth="1" style="3"/>
+    <col min="11" max="21" width="8.793388" customWidth="1" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:19">
+      <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="25" t="n">
+        <v>45938.7034722222234</v>
+      </c>
+      <c r="J1" s="25"/>
+      <c r="O1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="O2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="O3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="26" t="n">
+        <v>45920</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="S4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="S5" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="7" spans="1:10">
+      <c r="A7" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="11" spans="1:10">
+      <c r="A11" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="24"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="17"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="18"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="34">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="A13:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="A16:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="A19:J20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="A22:J46"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="F1" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$O$2:$O$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:E5" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$P$2:$P$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5:J5" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C8:E8" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$R$2:$R$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="H8:J8" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$S$2:$S$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.393750" right="0.393750" top="0.747917" bottom="0.393750" header="0.315278" footer="0.315278"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:S46"/>
+  <sheetFormatPr defaultRowHeight="21"/>
+  <cols>
+    <col min="1" max="10" width="8.793388" customWidth="1" style="3"/>
+    <col min="11" max="21" width="8.793388" customWidth="1" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:19">
+      <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="25" t="n">
+        <v>45938.7034722222234</v>
+      </c>
+      <c r="J1" s="25"/>
+      <c r="O1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="O2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="O3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="26" t="n">
+        <v>45927</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="S4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="S5" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="7" spans="1:10">
+      <c r="A7" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="11" spans="1:10">
+      <c r="A11" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="24"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="17"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="18"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="34">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="A13:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="A16:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="A19:J20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="A22:J46"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="F1" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$O$2:$O$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:E5" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$P$2:$P$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5:J5" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C8:E8" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$R$2:$R$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="H8:J8" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$S$2:$S$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.393750" right="0.393750" top="0.747917" bottom="0.393750" header="0.315278" footer="0.315278"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:S46"/>
+  <sheetFormatPr defaultRowHeight="21"/>
+  <cols>
+    <col min="1" max="10" width="8.793388" customWidth="1" style="3"/>
+    <col min="11" max="21" width="8.793388" customWidth="1" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:19">
+      <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="25" t="n">
+        <v>45938.7034722222234</v>
+      </c>
+      <c r="J1" s="25"/>
+      <c r="O1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="O2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="O3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="26" t="n">
+        <v>45927</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="S4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="S5" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="7" spans="1:10">
+      <c r="A7" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="11" spans="1:10">
+      <c r="A11" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="24"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="17"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="18"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="34">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="A13:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="A16:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="A19:J20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="A22:J46"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="F1" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$O$2:$O$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:E5" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$P$2:$P$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5:J5" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C8:E8" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$R$2:$R$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="H8:J8" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$S$2:$S$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.393750" right="0.393750" top="0.747917" bottom="0.393750" header="0.315278" footer="0.315278"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:S46"/>
+  <sheetFormatPr defaultRowHeight="21"/>
+  <cols>
+    <col min="1" max="10" width="8.793388" customWidth="1" style="3"/>
+    <col min="11" max="21" width="8.793388" customWidth="1" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:19">
+      <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="25" t="n">
+        <v>45942.6756944444423</v>
+      </c>
+      <c r="J1" s="25"/>
+      <c r="O1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="O2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="O3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="26" t="n">
+        <v>45942</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="S4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="S5" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="7" spans="1:10">
+      <c r="A7" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="11" spans="1:10">
+      <c r="A11" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="24"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="17"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="18"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="34">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="A13:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="A16:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="A19:J20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="A22:J46"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="F1" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$O$2:$O$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:E5" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$P$2:$P$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5:J5" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C8:E8" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$R$2:$R$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="H8:J8" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$S$2:$S$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.393750" right="0.393750" top="0.747917" bottom="0.393750" header="0.315278" footer="0.315278"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:S46"/>
+  <sheetFormatPr defaultRowHeight="21"/>
+  <cols>
+    <col min="1" max="10" width="8.793388" customWidth="1" style="3"/>
+    <col min="11" max="21" width="8.793388" customWidth="1" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:19">
+      <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="25" t="n">
+        <v>45942.6756944444423</v>
+      </c>
+      <c r="J1" s="25"/>
+      <c r="O1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="O2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="O3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="26" t="n">
+        <v>45942</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="S4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="S5" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="7" spans="1:10">
+      <c r="A7" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="11" spans="1:10">
+      <c r="A11" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="24"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="17"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="18"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="34">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="A13:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="A16:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="A19:J20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="A22:J46"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="F1" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$O$2:$O$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:E5" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$P$2:$P$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5:J5" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C8:E8" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$R$2:$R$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="H8:J8" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$S$2:$S$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.393750" right="0.393750" top="0.747917" bottom="0.393750" header="0.315278" footer="0.315278"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:S46"/>
+  <sheetFormatPr defaultRowHeight="21"/>
+  <cols>
+    <col min="1" max="10" width="8.793388" customWidth="1" style="3"/>
+    <col min="11" max="21" width="8.793388" customWidth="1" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:19">
+      <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="25" t="n">
+        <v>45950.9236111111095</v>
+      </c>
+      <c r="J1" s="25"/>
+      <c r="O1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="O2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="O3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="26" t="n">
+        <v>45950</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="S4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="S5" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="7" spans="1:10">
+      <c r="A7" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="11" spans="1:10">
+      <c r="A11" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="24"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="17"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="18"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="34">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="A13:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="A16:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="A19:J20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="A22:J46"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="F1" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$O$2:$O$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:E5" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$P$2:$P$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5:J5" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C8:E8" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$R$2:$R$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="H8:J8" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" view="0">
+      <formula1>$S$2:$S$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1760967717" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.393750" right="0.393750" top="0.747917" bottom="0.393750" header="0.315278" footer="0.315278"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1760967717" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1760967717" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1760967717" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/Assets/Planning/QA/Revenger_BTL.xlsx
+++ b/Assets/Planning/QA/Revenger_BTL.xlsx
@@ -5,7 +5,7 @@
   <fileSharing readOnlyRecommended="0" userName="autoa"/>
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="8" xWindow="240" yWindow="60" windowWidth="22050" windowHeight="9885" tabRatio="500"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="22050" windowHeight="9885" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="1" r:id="rId4"/>
@@ -22,17 +22,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1762521293" val="1228" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1762521293" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1762521293" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1762521293"/>
+      <pm:revision xmlns:pm="smNativeData" day="1763127194" val="1228" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1763127194" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1763127194" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1763127194"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -106,7 +106,7 @@
     <t>Issue No.</t>
   </si>
   <si>
-    <t>803c04a - 12</t>
+    <t>dd2a22d - 21</t>
   </si>
   <si>
     <t>TD</t>
@@ -154,9 +154,6 @@
     <t>Replay</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>Frequency</t>
   </si>
   <si>
@@ -175,10 +172,10 @@
     <t>Detail</t>
   </si>
   <si>
-    <t>적 제압시 무반응 현상</t>
+    <t>문이 열리지 않고 테드리만 열리는 버그</t>
   </si>
   <si>
-    <t>Home에서 무기 선택후 저택 진입 후 적의 후방에서 제압시 적이 쓰러지지 않고 그대로 멈춰버림</t>
+    <t xml:space="preserve">문이 제대로 열리지 않고 테두리로 추정되는 오브젝트만 열려 진행이 불가함. </t>
   </si>
   <si>
     <t>Replay</t>
@@ -187,55 +184,55 @@
     <t>Comment</t>
   </si>
   <si>
-    <t>Animator파일의 검토가 필요</t>
+    <t>문 프리팹에 문제가 있던 것으로 판단</t>
   </si>
   <si>
     <t>Steel shot</t>
   </si>
   <si>
-    <t>803c04a - 13</t>
+    <t>dd2a22d - 22</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Home → Outside 씬 이동 버그</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Home씬에서 미션을 시작했을 시 야외 맵으로 이동시 플레이어 프리팹이 제대로 생성되지 않는 버그 발생</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 플레이어 프리팹이 씬으로 제대로 이송되도록 확인해야함 (급히 수정됨)</t>
+  </si>
+  <si>
+    <t>dd2a22d - 23</t>
+  </si>
+  <si>
+    <t>라이터 아이템 획득 불가 버그</t>
+  </si>
+  <si>
+    <t>drawing 퍼즐을 진행하기 위한 라이터 오브젝트(아이템)가 상호작용 키로 집어지지 않음</t>
+  </si>
+  <si>
+    <t>해당 라이터 오브젝트의 레이어, 혹은 코드 충돌이 있는 것으로 판단</t>
+  </si>
+  <si>
+    <t>Villan - A  공격시 동작 무한 반복 버그</t>
+  </si>
+  <si>
+    <t>무기를 꺼내고 Villan - A를 공격시 좌클릭을 연타할시 캐릭터의 공격 애니메이션이 반복되는 버그가 발생함.</t>
+  </si>
+  <si>
+    <t>주인공의 공격시스템, 애니메이션(animator) 파일을 검포해볼 필요가 있음.</t>
+  </si>
+  <si>
+    <t>7e18ef3 - 16</t>
   </si>
   <si>
     <t>Design</t>
   </si>
   <si>
     <t>엄기영</t>
-  </si>
-  <si>
-    <t>휴게실 벽 통과 버그</t>
-  </si>
-  <si>
-    <t>휴게실을 감싸는 벽을 바깥쪽에서 기둥 안쪽으로 진입시 벽을 그대로 통과해 휴게실 안으로 들어갈 수 있음</t>
-  </si>
-  <si>
-    <t>휴게실을 감싸는 벽을 수정해야할 필요가 있음</t>
-  </si>
-  <si>
-    <t>803c04a - 14</t>
-  </si>
-  <si>
-    <t>임무성공 - Home 복귀 버튼 누락</t>
-  </si>
-  <si>
-    <t>미션 클리어 후 Home으로 복귀하기 위한 버튼의 모습이 누락되있음</t>
-  </si>
-  <si>
-    <t>적군 Animator 파일의 검토가 필요</t>
-  </si>
-  <si>
-    <t>803c04a - 15</t>
-  </si>
-  <si>
-    <t>Study 퍼즐 인벤토리 책 아이템 누락</t>
-  </si>
-  <si>
-    <t>Study 퍼즐에 필요한 책을 확보 후 인벤토리에 책이 나오지 않는 버그 발생</t>
-  </si>
-  <si>
-    <t>인벤토리 코드를 다시 살펴볼 필요가 있음</t>
-  </si>
-  <si>
-    <t>7e18ef3 - 16</t>
   </si>
   <si>
     <t>경비원이 문 안으로 들어오지 못하는 버그</t>
@@ -247,56 +244,7 @@
     <t>문 사이에도 이동 범위를 따로 추가해 넣을 필요가 있음</t>
   </si>
   <si>
-    <t>7e18ef3 - 17</t>
-  </si>
-  <si>
-    <t>외부 공간 일부 오브젝트에 대한 적 npc 이동범위 수정 요청</t>
-  </si>
-  <si>
-    <t>건물 외부에 있는 몇몇 오브젝트 (나무, 분재 등) 에 대해 이동범위 공간의 마감이 제대로 완료되지 않아 
-적군 npc의 이동 문제가 있음</t>
-  </si>
-  <si>
-    <t>건물 외부 오브젝트에 대한 이동범위 마감이 필요</t>
-  </si>
-  <si>
-    <t>7e18ef3 - 18</t>
-  </si>
-  <si>
-    <t>외부 적군이 이동경로 이동중 뒤돌아 볼때 덜덜거리는 버그</t>
-  </si>
-  <si>
-    <t>외부 적군이 이동경로 이동중 뒤돌아 볼때 가끔씩 모션이 덜덜거리는 버그가 존재함.</t>
-  </si>
-  <si>
-    <t>적군 이동 경로를 다시 확인해보거나 이동범위의 추가 마감작업이 필요함</t>
-  </si>
-  <si>
-    <t>7e18ef3 - 19</t>
-  </si>
-  <si>
-    <t>외부건물 거치블럭 판정 없음</t>
-  </si>
-  <si>
-    <t>건물 외부에서 건물을 올려주는 블럭의 물리판정이 존재하지 않아 플레이어가 통과하는 버그 발견</t>
-  </si>
-  <si>
     <t>7e18ef3</t>
-  </si>
-  <si>
-    <t>건물 콜리전 추가 작업이 필요함</t>
-  </si>
-  <si>
-    <t>7e18ef3 - 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">방문 과도회전 버그 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">방문을 미리 열어두고 적군에게 쫒길 시 적군이 문을 여는 행동 때문에 문이 추가적으로 90도 또 돌아가는 버그 </t>
-  </si>
-  <si>
-    <t>문의 상호작용에 대한 버그를 다시 조사해야할 필요가 있음.</t>
   </si>
 </sst>
 </file>
@@ -316,7 +264,7 @@
     <numFmt numFmtId="14" formatCode="M/D/YYYY"/>
     <numFmt numFmtId="165" formatCode="MM/DD"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -325,7 +273,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -340,7 +288,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -356,7 +304,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="180" lang="default"/>
             <pm:cs face="Times New Roman" sz="180" lang="default"/>
             <pm:ea face="SimSun" sz="180" lang="default"/>
@@ -373,7 +321,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -388,7 +336,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default"/>
             <pm:cs face="Times New Roman" sz="180" lang="default"/>
             <pm:ea face="SimSun" sz="180" lang="default"/>
@@ -404,7 +352,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
@@ -420,7 +368,7 @@
       <sz val="12"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="240" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="240" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="240" lang="default" weight="bold"/>
@@ -437,7 +385,7 @@
       <sz val="6"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="120" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="120" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="120" lang="default" weight="bold"/>
@@ -453,7 +401,7 @@
       <sz val="6"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="120" lang="default"/>
             <pm:cs face="Times New Roman" sz="120" lang="default"/>
             <pm:ea face="SimSun" sz="120" lang="default"/>
@@ -469,7 +417,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
@@ -484,7 +432,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default"/>
             <pm:cs face="Times New Roman" sz="160" lang="default"/>
             <pm:ea face="SimSun" sz="160" lang="default"/>
@@ -501,7 +449,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -519,25 +467,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
-            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
-            <pm:cs face="맑은 고딕" sz="220" lang="default"/>
-            <pm:ea face="맑은 고딕" sz="220" lang="default"/>
-            <hyperlink type="5" url="" location="'5'!A1" text=""/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -555,7 +485,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -573,25 +503,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
-            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
-            <pm:cs face="맑은 고딕" sz="220" lang="default"/>
-            <pm:ea face="맑은 고딕" sz="220" lang="default"/>
-            <hyperlink type="5" url="" location="'9-1'!A1" text=""/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -609,7 +521,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -627,7 +539,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -645,7 +557,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -663,7 +575,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -681,7 +593,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -699,7 +611,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -717,7 +629,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -735,7 +647,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -753,7 +665,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1762521293" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -763,7 +675,7 @@
       </extLst>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -776,7 +688,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1762521293" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1763127194" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -790,7 +702,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1762521293" type="1" fgLvl="100" fgClr="00D8D8D8" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1763127194" type="1" fgLvl="100" fgClr="00D8D8D8" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -801,7 +713,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1762521293" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1763127194" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -839,13 +751,24 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1762521293" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1763127194" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8D8D8"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1763127194" type="1" fgLvl="100" fgClr="00D8D8D8" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left style="none">
         <color rgb="FF000000"/>
@@ -861,7 +784,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293"/>
+          <pm:border xmlns:pm="smNativeData" id="1763127194"/>
         </ext>
       </extLst>
     </border>
@@ -880,7 +803,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293"/>
+          <pm:border xmlns:pm="smNativeData" id="1763127194"/>
         </ext>
       </extLst>
     </border>
@@ -899,7 +822,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293">
+          <pm:border xmlns:pm="smNativeData" id="1763127194">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -923,7 +846,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293">
+          <pm:border xmlns:pm="smNativeData" id="1763127194">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -947,7 +870,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293">
+          <pm:border xmlns:pm="smNativeData" id="1763127194">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -971,7 +894,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293">
+          <pm:border xmlns:pm="smNativeData" id="1763127194">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
         </ext>
@@ -992,7 +915,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293">
+          <pm:border xmlns:pm="smNativeData" id="1763127194">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1014,7 +937,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293">
+          <pm:border xmlns:pm="smNativeData" id="1763127194">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
         </ext>
@@ -1035,7 +958,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293">
+          <pm:border xmlns:pm="smNativeData" id="1763127194">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1057,7 +980,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293">
+          <pm:border xmlns:pm="smNativeData" id="1763127194">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1079,7 +1002,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293">
+          <pm:border xmlns:pm="smNativeData" id="1763127194">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1101,7 +1024,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293">
+          <pm:border xmlns:pm="smNativeData" id="1763127194">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1124,7 +1047,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293">
+          <pm:border xmlns:pm="smNativeData" id="1763127194">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1146,7 +1069,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293">
+          <pm:border xmlns:pm="smNativeData" id="1763127194">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1169,7 +1092,26 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1762521293"/>
+          <pm:border xmlns:pm="smNativeData" id="1763127194"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1763127194"/>
         </ext>
       </extLst>
     </border>
@@ -1279,10 +1221,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1306,13 +1254,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1323,10 +1265,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1762521293" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1763127194" count="1">
         <pm:charStyle name="보통" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1762521293" count="2">
+      <pm:colors xmlns:pm="smNativeData" id="1763127194" count="2">
         <pm:color name="색: 24" rgb="D8D8D8"/>
         <pm:color name="색: 25" rgb="BFBFBF"/>
       </pm:colors>
@@ -1340,15 +1282,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>269875</xdr:rowOff>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>96520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
+      <xdr:colOff>368300</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>29210</xdr:rowOff>
+      <xdr:rowOff>109855</xdr:rowOff>
     </xdr:to>
     <xdr:pic macro="">
       <xdr:nvPicPr>
@@ -1357,7 +1299,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_zfANaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAUAAAAAAAAAP4DAAAjAAAACQAAAG8A8wMAAAAAxiAAAIIpAAB7FwAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_mi8XaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAADGQt+GHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAG4BkAAjAAAACQAAAKEBLgKWAAAAXyEAABYnAABhFwAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1370,8 +1312,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="5327650"/>
-          <a:ext cx="6747510" cy="3816985"/>
+          <a:off x="95250" y="5424805"/>
+          <a:ext cx="6353810" cy="3800475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1397,23 +1339,22 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>260985</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>96520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>267335</xdr:rowOff>
+      <xdr:colOff>528320</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>116205</xdr:rowOff>
     </xdr:to>
     <xdr:pic macro="">
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림1"/>
+        <xdr:cNvPr id="2" name="그림1"/>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_zfANaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAUAAAAAAAAANwDAAAhAAAACQAAAPQD8wAAAAAAuCAAAGQmAACsFQAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_mi8XaRMAAAAlAAAAEQAAAI8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAABgAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAG4BAAAmAAAACQAAALcBIQMAAAAAXyEAAKgoAABpHAAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1426,59 +1367,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="5318760"/>
-          <a:ext cx="6240780" cy="3522980"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>429260</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>251460</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic macro="">
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_zfANaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAiAAAAAAAAACQAAAAtAAAACAAAALgDiwIAAAAAeDYAAOQjAADLEwAAAAAAAA=="/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="8854440"/>
-          <a:ext cx="5834380" cy="3217545"/>
+          <a:off x="0" y="5424805"/>
+          <a:ext cx="6609080" cy="4618355"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1508,19 +1398,18 @@
       <xdr:rowOff>29210</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>652145</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>53975</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>4445</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic macro="">
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="그림1"/>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_zfANaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAKAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAG8AAAAkAAAACQAAAMwA3AMAAAAA9SAAAGspAAAdGQAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_mi8XaRMAAAAlAAAAEQAAAI8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAG4AAAAfAAAACgAAAAAABwAAAAAA9SAAAJcpAAB2EAAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1534,7 +1423,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="5357495"/>
-          <a:ext cx="6732905" cy="4082415"/>
+          <a:ext cx="6760845" cy="2675890"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1559,62 +1448,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>29210</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>646430</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>220345</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic macro="">
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_zfANaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAG8AAAAqAAAACQAAAEID1AMAAAAA9SAAAGIpAAAfJAAAAAAAAA=="/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="5357495"/>
-          <a:ext cx="6727190" cy="5871845"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>635</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>135255</xdr:rowOff>
@@ -1632,7 +1465,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_zfANaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAAACAQAjAAAACQAAAAID4AMBAAAAnCEAAG4pAAC3FwAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_mi8XaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAAACAQAjAAAACQAAAAED4AMBAAAAnCEAAG4pAAC3FwAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1666,119 +1499,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>222250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>212725</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic macro="">
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_zfANaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAQAAAEkDFgIoAAAACAAAAAADQgFTBgAAJSIAADwcAACAHwAAAAAAAA=="/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1028065" y="5550535"/>
-          <a:ext cx="4589780" cy="5120640"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>29210</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>529590</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>130175</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic macro="">
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_zfANaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAG4AAAAlAAAACQAAAOwBIwMAAAAA9SAAAKooAAA/GwAAAAAAAA=="/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="5357495"/>
-          <a:ext cx="6610350" cy="4429125"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1800,7 +1521,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_zfANaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAWAAAAAAAAAJIDDgAlAAAACQAAACcDawMPAAAA7SMAAOYoAADKGAAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_mi8XaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAWAAAAAAAAAJEDDgAlAAAACQAAACgDawMPAAAA7SMAAOYoAADKGAAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -2108,7 +1829,7 @@
       </c>
       <c r="G1" s="14">
         <f aca="1">TODAY()</f>
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="H1" s="14"/>
     </row>
@@ -2156,11 +1877,11 @@
       </c>
       <c r="B4" s="9">
         <f>'12'!C4</f>
-        <v>45957</v>
+        <v>45975</v>
       </c>
       <c r="C4" s="8" t="str">
         <f>'12'!C3</f>
-        <v>803c04a - 12</v>
+        <v>dd2a22d - 21</v>
       </c>
       <c r="D4" s="8" t="str">
         <f>'12'!C9</f>
@@ -2172,7 +1893,7 @@
       </c>
       <c r="F4" s="12" t="str">
         <f>'12'!C12</f>
-        <v>적 제압시 무반응 현상</v>
+        <v>문이 열리지 않고 테드리만 열리는 버그</v>
       </c>
       <c r="G4" s="8" t="str">
         <f>'12'!H4</f>
@@ -2189,23 +1910,23 @@
       </c>
       <c r="B5" s="9">
         <f>'13'!C4</f>
-        <v>45957</v>
+        <v>45975</v>
       </c>
       <c r="C5" s="8" t="str">
         <f>'13'!C3</f>
-        <v>803c04a - 13</v>
+        <v>dd2a22d - 22</v>
       </c>
       <c r="D5" s="8" t="str">
         <f>'13'!C9</f>
-        <v>Design</v>
+        <v>Scripts</v>
       </c>
       <c r="E5" s="8" t="str">
         <f>'13'!C5</f>
-        <v>Mid</v>
+        <v>High</v>
       </c>
       <c r="F5" s="12" t="str">
         <f>'13'!C12</f>
-        <v>휴게실 벽 통과 버그</v>
+        <v>Home → Outside 씬 이동 버그</v>
       </c>
       <c r="G5" s="8" t="str">
         <f>'12'!H4</f>
@@ -2213,7 +1934,7 @@
       </c>
       <c r="H5" s="8" t="str">
         <f>'13'!H9</f>
-        <v>엄기영</v>
+        <v>이민기</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2222,11 +1943,11 @@
       </c>
       <c r="B6" s="9">
         <f>'14'!C4</f>
-        <v>45957</v>
+        <v>45975</v>
       </c>
       <c r="C6" s="8" t="str">
         <f>'14'!C3</f>
-        <v>803c04a - 14</v>
+        <v>dd2a22d - 23</v>
       </c>
       <c r="D6" s="8" t="str">
         <f>'14'!C9</f>
@@ -2234,11 +1955,11 @@
       </c>
       <c r="E6" s="8" t="str">
         <f>'14'!C5</f>
-        <v>Low</v>
+        <v>Mid</v>
       </c>
       <c r="F6" s="12" t="str">
         <f>'14'!C12</f>
-        <v>임무성공 - Home 복귀 버튼 누락</v>
+        <v>라이터 아이템 획득 불가 버그</v>
       </c>
       <c r="G6" s="8" t="str">
         <f>'12'!H4</f>
@@ -2255,11 +1976,11 @@
       </c>
       <c r="B7" s="9">
         <f>'15'!C4</f>
-        <v>45957</v>
+        <v>45975</v>
       </c>
       <c r="C7" s="8" t="str">
         <f>'15'!C3</f>
-        <v>803c04a - 15</v>
+        <v>dd2a22d - 23</v>
       </c>
       <c r="D7" s="8" t="str">
         <f>'15'!C9</f>
@@ -2267,11 +1988,11 @@
       </c>
       <c r="E7" s="8" t="str">
         <f>'15'!C5</f>
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F7" s="12" t="str">
         <f>'15'!C12</f>
-        <v>Study 퍼즐 인벤토리 책 아이템 누락</v>
+        <v>Villan - A  공격시 동작 무한 반복 버그</v>
       </c>
       <c r="G7" s="8" t="str">
         <f>'12'!H4</f>
@@ -2300,7 +2021,7 @@
       </c>
       <c r="E8" s="8" t="str">
         <f>'15'!C5</f>
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F8" s="12" t="str">
         <f>'16'!C12</f>
@@ -2316,136 +2037,44 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="32" t="n">
-        <v>17</v>
-      </c>
-      <c r="B9" s="9">
-        <f>'17'!C4</f>
-        <v>45968</v>
-      </c>
-      <c r="C9" s="8" t="str">
-        <f>'17'!C3</f>
-        <v>7e18ef3 - 17</v>
-      </c>
-      <c r="D9" s="8" t="str">
-        <f>'17'!C9</f>
-        <v>Design</v>
-      </c>
-      <c r="E9" s="8" t="str">
-        <f>'17'!C5</f>
-        <v>Low</v>
-      </c>
-      <c r="F9" s="12" t="str">
-        <f>'17'!C12</f>
-        <v>외부 공간 일부 오브젝트에 대한 적 npc 이동범위 수정 요청</v>
-      </c>
-      <c r="G9" s="8" t="str">
-        <f>'12'!H4</f>
-        <v>김사윤</v>
-      </c>
-      <c r="H9" s="8" t="str">
-        <f>'17'!H9</f>
-        <v>엄기영</v>
-      </c>
+      <c r="A9" s="32"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="B10" s="9">
-        <f>'18'!C4</f>
-        <v>45968</v>
-      </c>
-      <c r="C10" s="8" t="str">
-        <f>'18'!C3</f>
-        <v>7e18ef3 - 18</v>
-      </c>
-      <c r="D10" s="8" t="str">
-        <f>'18'!C9</f>
-        <v>Scripts</v>
-      </c>
-      <c r="E10" s="8" t="str">
-        <f>'18'!C5</f>
-        <v>Mid</v>
-      </c>
-      <c r="F10" s="12" t="str">
-        <f>'18'!C12</f>
-        <v>외부 적군이 이동경로 이동중 뒤돌아 볼때 덜덜거리는 버그</v>
-      </c>
-      <c r="G10" s="8" t="str">
-        <f>'12'!H4</f>
-        <v>김사윤</v>
-      </c>
-      <c r="H10" s="8" t="str">
-        <f>'18'!H9</f>
-        <v>이민기</v>
-      </c>
+      <c r="A10" s="33"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="29" t="n">
-        <v>19</v>
-      </c>
-      <c r="B11" s="9">
-        <f>'19'!C4</f>
-        <v>45968</v>
-      </c>
-      <c r="C11" s="8" t="str">
-        <f>'19'!C3</f>
-        <v>7e18ef3 - 19</v>
-      </c>
-      <c r="D11" s="9" t="str">
-        <f>'19'!C9</f>
-        <v>Design</v>
-      </c>
-      <c r="E11" s="8" t="str">
-        <f>'19'!C5</f>
-        <v>Low</v>
-      </c>
-      <c r="F11" s="12" t="str">
-        <f>'19'!C12</f>
-        <v>외부건물 거치블럭 판정 없음</v>
-      </c>
-      <c r="G11" s="8" t="str">
-        <f>'12'!H4</f>
-        <v>김사윤</v>
-      </c>
-      <c r="H11" s="9" t="str">
-        <f>'19'!H9</f>
-        <v>엄기영</v>
-      </c>
+      <c r="A11" s="29"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="B12" s="9">
-        <f>'20'!C4</f>
-        <v>45968</v>
-      </c>
-      <c r="C12" s="8" t="str">
-        <f>'20'!C3</f>
-        <v>7e18ef3 - 20</v>
-      </c>
-      <c r="D12" s="8" t="str">
-        <f>'20'!C9</f>
-        <v>Scripts</v>
-      </c>
-      <c r="E12" s="8" t="str">
-        <f>'20'!C5</f>
-        <v>Mid</v>
-      </c>
-      <c r="F12" s="12" t="str">
-        <f>'20'!C12</f>
-        <v>방문 과도회전 버그 </v>
-      </c>
-      <c r="G12" s="8" t="str">
-        <f>'12'!H4</f>
-        <v>김사윤</v>
-      </c>
-      <c r="H12" s="8" t="str">
-        <f>'20'!H9</f>
-        <v>이민기</v>
-      </c>
+      <c r="A12" s="43"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="34"/>
@@ -2610,7 +2239,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1762521293" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2619,16 +2248,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1762521293" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -2710,9 +2339,7 @@
         <v>23</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="8" t="s">
-        <v>84</v>
-      </c>
+      <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
@@ -2741,9 +2368,7 @@
         <v>30</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="26" t="n">
-        <v>45968</v>
-      </c>
+      <c r="C4" s="26"/>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
@@ -2813,7 +2438,7 @@
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
@@ -2824,28 +2449,24 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="9" t="s">
-        <v>43</v>
-      </c>
+      <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="9" t="s">
-        <v>45</v>
-      </c>
+      <c r="H9" s="9"/>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2862,9 +2483,7 @@
         <v>38</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30" t="s">
-        <v>85</v>
-      </c>
+      <c r="C12" s="30"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
@@ -2874,9 +2493,7 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31" t="s">
-        <v>86</v>
-      </c>
+      <c r="A13" s="31"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -2901,7 +2518,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -2939,7 +2556,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -2952,9 +2569,7 @@
       <c r="J18" s="24"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="15" t="s">
-        <v>87</v>
-      </c>
+      <c r="A19" s="15"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
@@ -2979,7 +2594,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -3348,7 +2963,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1762521293" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -3357,17 +2972,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1762521293" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -3396,7 +3011,7 @@
         <v>11</v>
       </c>
       <c r="I1" s="25" t="n">
-        <v>45950.9236111111095</v>
+        <v>45975.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
@@ -3481,7 +3096,7 @@
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45957</v>
+        <v>45975</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
@@ -3547,12 +3162,12 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
@@ -3563,20 +3178,20 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -3584,7 +3199,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3602,7 +3217,7 @@
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -3614,7 +3229,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -3640,7 +3255,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -3678,7 +3293,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -3692,7 +3307,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -3718,7 +3333,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -4087,7 +3702,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1762521293" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -4096,17 +3711,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1762521293" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -4135,7 +3750,7 @@
         <v>11</v>
       </c>
       <c r="I1" s="25" t="n">
-        <v>45950.9236111111095</v>
+        <v>45975.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
@@ -4189,7 +3804,7 @@
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -4220,7 +3835,7 @@
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45957</v>
+        <v>45975</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
@@ -4248,7 +3863,7 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -4286,36 +3901,36 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -4323,7 +3938,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4341,7 +3956,7 @@
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -4353,7 +3968,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="31" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -4379,7 +3994,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -4417,7 +4032,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -4431,7 +4046,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -4457,7 +4072,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -4826,7 +4441,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1762521293" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -4835,17 +4450,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1762521293" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -4874,7 +4489,7 @@
         <v>11</v>
       </c>
       <c r="I1" s="25" t="n">
-        <v>45950.9236111111095</v>
+        <v>45975.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
@@ -4928,7 +4543,7 @@
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -4959,7 +4574,7 @@
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45957</v>
+        <v>45975</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
@@ -4987,7 +4602,7 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -5025,12 +4640,12 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
@@ -5041,20 +4656,20 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -5062,7 +4677,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -5080,7 +4695,7 @@
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="30" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -5092,7 +4707,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -5118,7 +4733,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -5156,7 +4771,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -5170,7 +4785,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -5196,7 +4811,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -5565,7 +5180,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1762521293" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -5574,17 +5189,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1762521293" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -5667,7 +5282,7 @@
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -5698,7 +5313,7 @@
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45957</v>
+        <v>45975</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
@@ -5726,7 +5341,7 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -5764,36 +5379,36 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -5801,7 +5416,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -5819,7 +5434,7 @@
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="30" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -5831,7 +5446,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="31" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -5857,7 +5472,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -5895,7 +5510,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -5909,7 +5524,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -5935,7 +5550,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -6304,7 +5919,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1762521293" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -6313,17 +5928,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
-  <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1762521293" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -6406,7 +6020,7 @@
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -6503,12 +6117,12 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
@@ -6519,20 +6133,20 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -6540,7 +6154,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6558,7 +6172,7 @@
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -6570,7 +6184,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -6596,7 +6210,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -6634,7 +6248,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -6648,7 +6262,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -6674,7 +6288,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -7043,7 +6657,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1762521293" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -7052,17 +6666,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1762521293" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -7144,9 +6758,7 @@
         <v>23</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="8" t="s">
-        <v>71</v>
-      </c>
+      <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
@@ -7175,9 +6787,7 @@
         <v>30</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="26" t="n">
-        <v>45968</v>
-      </c>
+      <c r="C4" s="26"/>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
@@ -7242,12 +6852,12 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
@@ -7258,28 +6868,24 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="9" t="s">
-        <v>54</v>
-      </c>
+      <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="9" t="s">
-        <v>55</v>
-      </c>
+      <c r="H9" s="9"/>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -7296,9 +6902,7 @@
         <v>38</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30" t="s">
-        <v>72</v>
-      </c>
+      <c r="C12" s="30"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
@@ -7308,9 +6912,7 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31" t="s">
-        <v>73</v>
-      </c>
+      <c r="A13" s="31"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -7335,7 +6937,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -7373,7 +6975,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -7386,9 +6988,7 @@
       <c r="J18" s="24"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="15" t="s">
-        <v>74</v>
-      </c>
+      <c r="A19" s="15"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
@@ -7413,7 +7013,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -7782,7 +7382,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1762521293" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -7791,17 +7391,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
-  <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1762521293" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -7883,9 +7482,7 @@
         <v>23</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
@@ -7914,18 +7511,14 @@
         <v>30</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="26" t="n">
-        <v>45968</v>
-      </c>
+      <c r="C4" s="26"/>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G4" s="11"/>
-      <c r="H4" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
@@ -7986,7 +7579,7 @@
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
@@ -7997,28 +7590,24 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="9" t="s">
-        <v>43</v>
-      </c>
+      <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="9" t="s">
-        <v>45</v>
-      </c>
+      <c r="H9" s="9"/>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -8035,9 +7624,7 @@
         <v>38</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30" t="s">
-        <v>76</v>
-      </c>
+      <c r="C12" s="30"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
@@ -8047,9 +7634,7 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31" t="s">
-        <v>77</v>
-      </c>
+      <c r="A13" s="31"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -8074,7 +7659,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -8112,7 +7697,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -8125,9 +7710,7 @@
       <c r="J18" s="24"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="15" t="s">
-        <v>78</v>
-      </c>
+      <c r="A19" s="15"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
@@ -8152,7 +7735,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -8521,7 +8104,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1762521293" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -8530,16 +8113,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1762521293" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -8621,9 +8204,7 @@
         <v>23</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="8" t="s">
-        <v>79</v>
-      </c>
+      <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
@@ -8652,9 +8233,7 @@
         <v>30</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="26" t="n">
-        <v>45968</v>
-      </c>
+      <c r="C4" s="26"/>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
@@ -8719,12 +8298,12 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
@@ -8735,28 +8314,24 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="9" t="s">
-        <v>54</v>
-      </c>
+      <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="9" t="s">
-        <v>55</v>
-      </c>
+      <c r="H9" s="9"/>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -8773,9 +8348,7 @@
         <v>38</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30" t="s">
-        <v>80</v>
-      </c>
+      <c r="C12" s="30"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
@@ -8785,9 +8358,7 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31" t="s">
-        <v>81</v>
-      </c>
+      <c r="A13" s="31"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -8812,7 +8383,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -8850,7 +8421,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -8863,9 +8434,7 @@
       <c r="J18" s="24"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="15" t="s">
-        <v>83</v>
-      </c>
+      <c r="A19" s="15"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
@@ -8890,7 +8459,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -9259,7 +8828,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1762521293" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -9268,17 +8837,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1762521293" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1762521293" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
-  <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1762521293" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/Assets/Planning/QA/Revenger_BTL.xlsx
+++ b/Assets/Planning/QA/Revenger_BTL.xlsx
@@ -22,17 +22,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1763127194" val="1228" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1763127194" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1763127194" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1763127194"/>
+      <pm:revision xmlns:pm="smNativeData" day="1763650637" val="1228" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1763650637" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1763650637" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1763650637"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="73">
   <si>
     <t>Date</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>Charger</t>
+  </si>
+  <si>
+    <t>더미</t>
   </si>
   <si>
     <t>Product</t>
@@ -106,7 +109,7 @@
     <t>Issue No.</t>
   </si>
   <si>
-    <t>dd2a22d - 21</t>
+    <t>473a238 - 25</t>
   </si>
   <si>
     <t>TD</t>
@@ -160,22 +163,22 @@
     <t>Category</t>
   </si>
   <si>
-    <t>Scripts</t>
+    <t>Design</t>
   </si>
   <si>
     <t>Charger</t>
   </si>
   <si>
-    <t>이민기</t>
+    <t>엄기영</t>
   </si>
   <si>
     <t>Detail</t>
   </si>
   <si>
-    <t>문이 열리지 않고 테드리만 열리는 버그</t>
+    <t>외부 건물 기둥에 콜리전 누락</t>
   </si>
   <si>
-    <t xml:space="preserve">문이 제대로 열리지 않고 테두리로 추정되는 오브젝트만 열려 진행이 불가함. </t>
+    <t>건물 기둥에 히트박스가 존재하지 않음</t>
   </si>
   <si>
     <t>Replay</t>
@@ -184,64 +187,67 @@
     <t>Comment</t>
   </si>
   <si>
-    <t>문 프리팹에 문제가 있던 것으로 판단</t>
+    <t>기둥에 히트박스 추가 요청</t>
   </si>
   <si>
     <t>Steel shot</t>
   </si>
   <si>
-    <t>dd2a22d - 22</t>
+    <t>473a238 - 26</t>
+  </si>
+  <si>
+    <t>Scripts</t>
+  </si>
+  <si>
+    <t>이민기</t>
+  </si>
+  <si>
+    <t>(디버그) 노클립 이후 퍼즐 시퀀스 버그</t>
+  </si>
+  <si>
+    <t>노클립사용 이후 퍼즐 이용시 하수구 퍼즐 시퀀스만 들어가지는 버그</t>
+  </si>
+  <si>
+    <t>상호작용이 해당 퍼즐로 목표가 잡혀있는데 다른곳으로 강제 이동되어 생긴 문제 (급히 수정됨)</t>
+  </si>
+  <si>
+    <t>473a238 - 27</t>
+  </si>
+  <si>
+    <t>갑자기 모든 경비원에게 발각 버그</t>
+  </si>
+  <si>
+    <t>뛰어다니면 가끔씩 모든 경비병에게 발각되는 버그가 있음</t>
+  </si>
+  <si>
+    <t>경비병에게 발각되는 기준을 확실히 알기가 어려워 원인 파악이 힘듬</t>
+  </si>
+  <si>
+    <t>473a238 - 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dress/Guest 퍼즐 클리어후에도 다이얼 UI 접근 가능 </t>
+  </si>
+  <si>
+    <t>Dress/Guest 퍼즐 클리어후에도 다이얼 UI 접근이 가능한 버그</t>
+  </si>
+  <si>
+    <t>의도 된것인지는 아직 파악이 안됨.</t>
+  </si>
+  <si>
+    <t>473a238 - 29</t>
+  </si>
+  <si>
+    <t>식당 퍼즐 ui 일시정지 UI 꼬임</t>
+  </si>
+  <si>
+    <t>식당 퍼즐 ui가 출력되는 동안 esc를 누를시 ui가 꼬임</t>
+  </si>
+  <si>
+    <t>퍼즐 Ui와 일시정지 Ui의 배치를 다시 해야함</t>
   </si>
   <si>
     <t>Yes</t>
-  </si>
-  <si>
-    <t>Home → Outside 씬 이동 버그</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Home씬에서 미션을 시작했을 시 야외 맵으로 이동시 플레이어 프리팹이 제대로 생성되지 않는 버그 발생</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 플레이어 프리팹이 씬으로 제대로 이송되도록 확인해야함 (급히 수정됨)</t>
-  </si>
-  <si>
-    <t>dd2a22d - 23</t>
-  </si>
-  <si>
-    <t>라이터 아이템 획득 불가 버그</t>
-  </si>
-  <si>
-    <t>drawing 퍼즐을 진행하기 위한 라이터 오브젝트(아이템)가 상호작용 키로 집어지지 않음</t>
-  </si>
-  <si>
-    <t>해당 라이터 오브젝트의 레이어, 혹은 코드 충돌이 있는 것으로 판단</t>
-  </si>
-  <si>
-    <t>Villan - A  공격시 동작 무한 반복 버그</t>
-  </si>
-  <si>
-    <t>무기를 꺼내고 Villan - A를 공격시 좌클릭을 연타할시 캐릭터의 공격 애니메이션이 반복되는 버그가 발생함.</t>
-  </si>
-  <si>
-    <t>주인공의 공격시스템, 애니메이션(animator) 파일을 검포해볼 필요가 있음.</t>
-  </si>
-  <si>
-    <t>7e18ef3 - 16</t>
-  </si>
-  <si>
-    <t>Design</t>
-  </si>
-  <si>
-    <t>엄기영</t>
-  </si>
-  <si>
-    <t>경비원이 문 안으로 들어오지 못하는 버그</t>
-  </si>
-  <si>
-    <t>방 사이간 이어지는 문을 통해 경비원이 주인공을 잡기 위해 들어오지 못하는 버그</t>
-  </si>
-  <si>
-    <t>문 사이에도 이동 범위를 따로 추가해 넣을 필요가 있음</t>
   </si>
   <si>
     <t>7e18ef3</t>
@@ -273,7 +279,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -288,7 +294,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -304,7 +310,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="180" lang="default"/>
             <pm:cs face="Times New Roman" sz="180" lang="default"/>
             <pm:ea face="SimSun" sz="180" lang="default"/>
@@ -321,7 +327,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -336,7 +342,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default"/>
             <pm:cs face="Times New Roman" sz="180" lang="default"/>
             <pm:ea face="SimSun" sz="180" lang="default"/>
@@ -352,7 +358,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
@@ -368,7 +374,7 @@
       <sz val="12"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="240" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="240" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="240" lang="default" weight="bold"/>
@@ -385,7 +391,7 @@
       <sz val="6"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="120" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="120" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="120" lang="default" weight="bold"/>
@@ -401,7 +407,7 @@
       <sz val="6"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="120" lang="default"/>
             <pm:cs face="Times New Roman" sz="120" lang="default"/>
             <pm:ea face="SimSun" sz="120" lang="default"/>
@@ -417,7 +423,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
@@ -432,7 +438,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default"/>
             <pm:cs face="Times New Roman" sz="160" lang="default"/>
             <pm:ea face="SimSun" sz="160" lang="default"/>
@@ -449,61 +455,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
-            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-            <hyperlink type="5" url="" location="'1'!A1" text="'1'!A1"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
-            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
-            <pm:cs face="맑은 고딕" sz="220" lang="default"/>
-            <pm:ea face="맑은 고딕" sz="220" lang="default"/>
-            <hyperlink type="5" url="" location="'6'!A1" text=""/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
-            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
-            <pm:cs face="맑은 고딕" sz="220" lang="default"/>
-            <pm:ea face="맑은 고딕" sz="220" lang="default"/>
-            <hyperlink type="5" url="" location="'7'!A1" text=""/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -521,7 +473,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -539,7 +491,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -557,7 +509,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -575,7 +527,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -593,7 +545,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -611,7 +563,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -629,7 +581,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -647,7 +599,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -665,7 +617,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763127194" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -674,8 +626,62 @@
         </ext>
       </extLst>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
+            <pm:cs face="맑은 고딕" sz="220" lang="default"/>
+            <pm:ea face="맑은 고딕" sz="220" lang="default"/>
+            <hyperlink type="5" url="" location="'17'!A1" text=""/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
+            <pm:cs face="맑은 고딕" sz="220" lang="default"/>
+            <pm:ea face="맑은 고딕" sz="220" lang="default"/>
+            <hyperlink type="5" url="" location="'18'!A1" text=""/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+            <pm:latin face="맑은 고딕" sz="220" lang="default"/>
+            <pm:cs face="맑은 고딕" sz="220" lang="default"/>
+            <pm:ea face="맑은 고딕" sz="220" lang="default"/>
+            <hyperlink type="5" url="" location="'19'!A1" text=""/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -688,7 +694,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1763127194" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1763650637" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -702,7 +708,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1763127194" type="1" fgLvl="100" fgClr="00D8D8D8" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1763650637" type="1" fgLvl="100" fgClr="00D8D8D8" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -713,7 +719,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1763127194" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1763650637" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -751,24 +757,13 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1763127194" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8D8D8"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1763127194" type="1" fgLvl="100" fgClr="00D8D8D8" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1763650637" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left style="none">
         <color rgb="FF000000"/>
@@ -784,7 +779,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194"/>
+          <pm:border xmlns:pm="smNativeData" id="1763650637"/>
         </ext>
       </extLst>
     </border>
@@ -803,7 +798,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194"/>
+          <pm:border xmlns:pm="smNativeData" id="1763650637"/>
         </ext>
       </extLst>
     </border>
@@ -822,7 +817,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194">
+          <pm:border xmlns:pm="smNativeData" id="1763650637">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -846,7 +841,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194">
+          <pm:border xmlns:pm="smNativeData" id="1763650637">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -870,7 +865,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194">
+          <pm:border xmlns:pm="smNativeData" id="1763650637">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -894,7 +889,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194">
+          <pm:border xmlns:pm="smNativeData" id="1763650637">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
         </ext>
@@ -915,7 +910,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194">
+          <pm:border xmlns:pm="smNativeData" id="1763650637">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -937,7 +932,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194">
+          <pm:border xmlns:pm="smNativeData" id="1763650637">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
         </ext>
@@ -958,7 +953,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194">
+          <pm:border xmlns:pm="smNativeData" id="1763650637">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -980,7 +975,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194">
+          <pm:border xmlns:pm="smNativeData" id="1763650637">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1002,7 +997,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194">
+          <pm:border xmlns:pm="smNativeData" id="1763650637">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1024,7 +1019,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194">
+          <pm:border xmlns:pm="smNativeData" id="1763650637">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1047,7 +1042,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194">
+          <pm:border xmlns:pm="smNativeData" id="1763650637">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1069,7 +1064,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194">
+          <pm:border xmlns:pm="smNativeData" id="1763650637">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1092,26 +1087,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763127194"/>
+          <pm:border xmlns:pm="smNativeData" id="1763650637"/>
         </ext>
       </extLst>
     </border>
@@ -1212,14 +1188,14 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1245,7 +1221,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1254,7 +1230,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1265,10 +1241,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1763127194" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1763650637" count="1">
         <pm:charStyle name="보통" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1763127194" count="2">
+      <pm:colors xmlns:pm="smNativeData" id="1763650637" count="2">
         <pm:color name="색: 24" rgb="D8D8D8"/>
         <pm:color name="색: 25" rgb="BFBFBF"/>
       </pm:colors>
@@ -1282,15 +1258,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>96520</xdr:rowOff>
+      <xdr:rowOff>37465</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>368300</xdr:colOff>
+      <xdr:colOff>666115</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>109855</xdr:rowOff>
+      <xdr:rowOff>64770</xdr:rowOff>
     </xdr:to>
     <xdr:pic macro="">
       <xdr:nvPicPr>
@@ -1299,7 +1275,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_mi8XaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAADGQt+GHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAG4BkAAjAAAACQAAAKEBLgKWAAAAXyEAABYnAABhFwAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_TSwfaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAYAgAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAI4AAAAjAAAACQAAAPUA8gMAAAAAAiEAAIEpAAB3FwAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1312,8 +1288,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="95250" y="5424805"/>
-          <a:ext cx="6353810" cy="3800475"/>
+          <a:off x="0" y="5365750"/>
+          <a:ext cx="6746875" cy="3814445"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1338,172 +1314,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>96520</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>528320</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>116205</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic macro="">
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림1"/>
-        <xdr:cNvPicPr>
-          <a:extLst>
-            <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_mi8XaRMAAAAlAAAAEQAAAI8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAABgAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAG4BAAAmAAAACQAAALcBIQMAAAAAXyEAAKgoAABpHAAAAAAAAA=="/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="5424805"/>
-          <a:ext cx="6609080" cy="4618355"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>29210</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>4445</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic macro="">
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림1"/>
-        <xdr:cNvPicPr>
-          <a:extLst>
-            <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_mi8XaRMAAAAlAAAAEQAAAI8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAG4AAAAfAAAACgAAAAAABwAAAAAA9SAAAJcpAAB2EAAAAAAAAA=="/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="5357495"/>
-          <a:ext cx="6760845" cy="2675890"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>635</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>135255</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>654685</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic macro="">
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_mi8XaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAAACAQAjAAAACQAAAAED4AMBAAAAnCEAAG4pAAC3FwAAAAAAAA=="/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="635" y="5463540"/>
-          <a:ext cx="6734810" cy="3855085"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>241300</xdr:rowOff>
@@ -1521,7 +1331,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_mi8XaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAWAAAAAAAAAJEDDgAlAAAACQAAACgDawMPAAAA7SMAAOYoAADKGAAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_TSwfaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAWAAAAAAAAAJEDDgAlAAAACQAAACgDawMPAAAA7SMAAOYoAADKGAAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1811,7 +1621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="7.297521" customWidth="1" style="7"/>
@@ -1829,7 +1639,7 @@
       </c>
       <c r="G1" s="14">
         <f aca="1">TODAY()</f>
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="H1" s="14"/>
     </row>
@@ -1872,28 +1682,28 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="38" t="n">
+      <c r="A4" s="35" t="n">
         <v>12</v>
       </c>
       <c r="B4" s="9">
         <f>'12'!C4</f>
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="C4" s="8" t="str">
         <f>'12'!C3</f>
-        <v>dd2a22d - 21</v>
+        <v>473a238 - 25</v>
       </c>
       <c r="D4" s="8" t="str">
         <f>'12'!C9</f>
-        <v>Scripts</v>
+        <v>Design</v>
       </c>
       <c r="E4" s="8" t="str">
         <f>'12'!C5</f>
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F4" s="12" t="str">
         <f>'12'!C12</f>
-        <v>문이 열리지 않고 테드리만 열리는 버그</v>
+        <v>외부 건물 기둥에 콜리전 누락</v>
       </c>
       <c r="G4" s="8" t="str">
         <f>'12'!H4</f>
@@ -1901,20 +1711,20 @@
       </c>
       <c r="H4" s="8" t="str">
         <f>'12'!H9</f>
-        <v>이민기</v>
+        <v>엄기영</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="39" t="n">
+      <c r="A5" s="36" t="n">
         <v>13</v>
       </c>
       <c r="B5" s="9">
         <f>'13'!C4</f>
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="C5" s="8" t="str">
         <f>'13'!C3</f>
-        <v>dd2a22d - 22</v>
+        <v>473a238 - 26</v>
       </c>
       <c r="D5" s="8" t="str">
         <f>'13'!C9</f>
@@ -1922,11 +1732,11 @@
       </c>
       <c r="E5" s="8" t="str">
         <f>'13'!C5</f>
-        <v>High</v>
+        <v>Mid</v>
       </c>
       <c r="F5" s="12" t="str">
         <f>'13'!C12</f>
-        <v>Home → Outside 씬 이동 버그</v>
+        <v>(디버그) 노클립 이후 퍼즐 시퀀스 버그</v>
       </c>
       <c r="G5" s="8" t="str">
         <f>'12'!H4</f>
@@ -1938,16 +1748,16 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="40" t="n">
+      <c r="A6" s="37" t="n">
         <v>14</v>
       </c>
       <c r="B6" s="9">
         <f>'14'!C4</f>
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="C6" s="8" t="str">
         <f>'14'!C3</f>
-        <v>dd2a22d - 23</v>
+        <v>473a238 - 27</v>
       </c>
       <c r="D6" s="8" t="str">
         <f>'14'!C9</f>
@@ -1959,7 +1769,7 @@
       </c>
       <c r="F6" s="12" t="str">
         <f>'14'!C12</f>
-        <v>라이터 아이템 획득 불가 버그</v>
+        <v>갑자기 모든 경비원에게 발각 버그</v>
       </c>
       <c r="G6" s="8" t="str">
         <f>'12'!H4</f>
@@ -1971,16 +1781,16 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="41" t="n">
+      <c r="A7" s="38" t="n">
         <v>15</v>
       </c>
       <c r="B7" s="9">
         <f>'15'!C4</f>
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="C7" s="8" t="str">
         <f>'15'!C3</f>
-        <v>dd2a22d - 23</v>
+        <v>473a238 - 28</v>
       </c>
       <c r="D7" s="8" t="str">
         <f>'15'!C9</f>
@@ -1988,11 +1798,11 @@
       </c>
       <c r="E7" s="8" t="str">
         <f>'15'!C5</f>
-        <v>Low</v>
+        <v>Mid</v>
       </c>
       <c r="F7" s="12" t="str">
         <f>'15'!C12</f>
-        <v>Villan - A  공격시 동작 무한 반복 버그</v>
+        <v>Dress/Guest 퍼즐 클리어후에도 다이얼 UI 접근 가능 </v>
       </c>
       <c r="G7" s="8" t="str">
         <f>'12'!H4</f>
@@ -2004,7 +1814,7 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="42" t="n">
+      <c r="A8" s="39" t="n">
         <v>16</v>
       </c>
       <c r="B8" s="9">
@@ -2013,19 +1823,19 @@
       </c>
       <c r="C8" s="8" t="str">
         <f>'16'!C3</f>
-        <v>7e18ef3 - 16</v>
+        <v>473a238 - 29</v>
       </c>
       <c r="D8" s="8" t="str">
         <f>'16'!C9</f>
-        <v>Design</v>
+        <v>Scripts</v>
       </c>
       <c r="E8" s="8" t="str">
-        <f>'15'!C5</f>
-        <v>Low</v>
+        <f>'16'!C5</f>
+        <v>Mid</v>
       </c>
       <c r="F8" s="12" t="str">
         <f>'16'!C12</f>
-        <v>경비원이 문 안으로 들어오지 못하는 버그</v>
+        <v>식당 퍼즐 ui 일시정지 UI 꼬임</v>
       </c>
       <c r="G8" s="8" t="str">
         <f>'12'!H4</f>
@@ -2033,11 +1843,11 @@
       </c>
       <c r="H8" s="8" t="str">
         <f>'16'!H9</f>
-        <v>엄기영</v>
+        <v>이민기</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="32"/>
+      <c r="A9" s="8"/>
       <c r="B9" s="9"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -2047,7 +1857,7 @@
       <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="33"/>
+      <c r="A10" s="8"/>
       <c r="B10" s="9"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -2057,17 +1867,17 @@
       <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="29"/>
+      <c r="A11" s="8"/>
       <c r="B11" s="9"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="9"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="12"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="9"/>
+      <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="43"/>
+      <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -2077,7 +1887,7 @@
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="34"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="9"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -2087,7 +1897,7 @@
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="35"/>
+      <c r="A14" s="32"/>
       <c r="B14" s="9"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -2097,7 +1907,7 @@
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="36"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="9"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -2107,7 +1917,7 @@
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="37"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="9"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -2207,7 +2017,9 @@
       <c r="H25" s="8"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="8"/>
+      <c r="A26" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="B26" s="9"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -2215,6 +2027,138 @@
       <c r="F26" s="12"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="41" t="n">
+        <v>17</v>
+      </c>
+      <c r="B27" s="9">
+        <f>'17'!C4</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="8">
+        <f>'17'!C3</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="8">
+        <f>'17'!C9</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="8" t="str">
+        <f>'17'!C5</f>
+        <v>Low</v>
+      </c>
+      <c r="F27" s="12">
+        <f>'17'!C12</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="str">
+        <f>'12'!H4</f>
+        <v>김사윤</v>
+      </c>
+      <c r="H27" s="8">
+        <f>'17'!H9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="B28" s="9">
+        <f>'18'!C4</f>
+        <v>0</v>
+      </c>
+      <c r="C28" s="8">
+        <f>'18'!C3</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="8">
+        <f>'18'!C9</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="8" t="str">
+        <f>'18'!C5</f>
+        <v>Mid</v>
+      </c>
+      <c r="F28" s="12">
+        <f>'18'!C12</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="8" t="str">
+        <f>'12'!H4</f>
+        <v>김사윤</v>
+      </c>
+      <c r="H28" s="8">
+        <f>'18'!H9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="B29" s="9">
+        <f>'19'!C4</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="8">
+        <f>'19'!C3</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="9">
+        <f>'19'!C9</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="8" t="str">
+        <f>'19'!C5</f>
+        <v>Low</v>
+      </c>
+      <c r="F29" s="12">
+        <f>'19'!C12</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="8" t="str">
+        <f>'12'!H4</f>
+        <v>김사윤</v>
+      </c>
+      <c r="H29" s="9">
+        <f>'19'!H9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="B30" s="9">
+        <f>'20'!C4</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="8">
+        <f>'20'!C3</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="8">
+        <f>'20'!C9</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="8" t="str">
+        <f>'20'!C5</f>
+        <v>Mid</v>
+      </c>
+      <c r="F30" s="12">
+        <f>'20'!C12</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="8" t="str">
+        <f>'12'!H4</f>
+        <v>김사윤</v>
+      </c>
+      <c r="H30" s="8">
+        <f>'20'!H9</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2227,19 +2171,19 @@
     <hyperlink ref="A6" location="'14'!A1"/>
     <hyperlink ref="A7" location="'15'!A1"/>
     <hyperlink ref="A8" location="'16'!A1"/>
-    <hyperlink ref="A9" location="'6'!A1"/>
-    <hyperlink ref="A10" location="'7'!A1"/>
-    <hyperlink ref="A11" location="'1'!A1"/>
-    <hyperlink ref="A12" location="'20'!A1"/>
     <hyperlink ref="A13" location="'9-2'!A1"/>
     <hyperlink ref="A14" location="'10-1'!A1"/>
     <hyperlink ref="A15" location="'10-2'!A1"/>
     <hyperlink ref="A16" location="'11'!A1"/>
+    <hyperlink ref="A27" location="'17'!A1"/>
+    <hyperlink ref="A28" location="'18'!A1"/>
+    <hyperlink ref="A29" location="'19'!A1"/>
+    <hyperlink ref="A30" location="'20'!A1"/>
   </hyperlinks>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2248,16 +2192,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -2277,37 +2221,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1" s="25" t="n">
         <v>45950.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -2319,24 +2263,24 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8"/>
@@ -2348,45 +2292,45 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26"/>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2395,27 +2339,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -2429,34 +2373,34 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9"/>
@@ -2466,7 +2410,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2480,10 +2424,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
@@ -2493,7 +2437,7 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -2518,7 +2462,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -2556,7 +2500,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -2594,7 +2538,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -2963,7 +2907,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2972,17 +2916,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -3002,37 +2946,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1" s="25" t="n">
         <v>45975.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3044,28 +2988,28 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -3075,47 +3019,47 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3124,27 +3068,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -3158,40 +3102,40 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -3199,7 +3143,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3213,11 +3157,11 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30" t="s">
-        <v>46</v>
+      <c r="C12" s="29" t="s">
+        <v>47</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -3228,8 +3172,8 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31" t="s">
-        <v>47</v>
+      <c r="A13" s="30" t="s">
+        <v>48</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -3255,7 +3199,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -3293,7 +3237,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -3307,7 +3251,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -3333,7 +3277,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -3702,7 +3646,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -3711,17 +3655,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -3741,37 +3685,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1" s="25" t="n">
         <v>45975.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3783,28 +3727,28 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -3814,47 +3758,47 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3863,27 +3807,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -3897,40 +3841,40 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -3938,7 +3882,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3952,11 +3896,11 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30" t="s">
-        <v>54</v>
+      <c r="C12" s="29" t="s">
+        <v>56</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -3967,8 +3911,8 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31" t="s">
-        <v>55</v>
+      <c r="A13" s="30" t="s">
+        <v>57</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -3994,7 +3938,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -4032,7 +3976,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -4046,7 +3990,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -4072,7 +4016,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -4441,7 +4385,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -4450,17 +4394,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
-  <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -4480,37 +4423,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1" s="25" t="n">
         <v>45975.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -4522,28 +4465,28 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -4553,47 +4496,47 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4602,27 +4545,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4636,40 +4579,40 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -4677,7 +4620,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4691,11 +4634,11 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30" t="s">
-        <v>58</v>
+      <c r="C12" s="29" t="s">
+        <v>60</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -4706,8 +4649,8 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31" t="s">
-        <v>59</v>
+      <c r="A13" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -4733,7 +4676,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -4771,7 +4714,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -4785,7 +4728,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -4811,7 +4754,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -5180,7 +5123,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -5189,17 +5132,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
-  <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -5219,37 +5161,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1" s="25" t="n">
         <v>45950.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -5261,28 +5203,28 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -5292,47 +5234,47 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -5341,27 +5283,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -5375,40 +5317,40 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -5416,7 +5358,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -5430,11 +5372,11 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30" t="s">
-        <v>61</v>
+      <c r="C12" s="29" t="s">
+        <v>64</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -5445,8 +5387,8 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31" t="s">
-        <v>62</v>
+      <c r="A13" s="30" t="s">
+        <v>65</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -5472,7 +5414,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -5510,7 +5452,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -5524,7 +5466,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -5550,7 +5492,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -5919,7 +5861,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -5928,16 +5870,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -5957,37 +5899,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1" s="25" t="n">
         <v>45950.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -5999,28 +5941,28 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -6030,24 +5972,24 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
@@ -6056,21 +5998,21 @@
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -6079,27 +6021,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -6113,40 +6055,40 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -6154,7 +6096,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6168,11 +6110,11 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30" t="s">
-        <v>67</v>
+      <c r="C12" s="29" t="s">
+        <v>68</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -6183,8 +6125,8 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31" t="s">
-        <v>68</v>
+      <c r="A13" s="30" t="s">
+        <v>69</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -6210,7 +6152,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -6248,7 +6190,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -6262,7 +6204,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -6288,7 +6230,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -6657,7 +6599,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -6666,17 +6608,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
-  <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -6696,37 +6637,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1" s="25" t="n">
         <v>45950.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -6738,24 +6679,24 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8"/>
@@ -6767,45 +6708,45 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26"/>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -6814,27 +6755,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -6848,34 +6789,34 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9"/>
@@ -6885,7 +6826,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6899,10 +6840,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
@@ -6912,7 +6853,7 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -6937,7 +6878,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -6975,7 +6916,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -7013,7 +6954,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -7382,7 +7323,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -7391,16 +7332,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -7420,37 +7361,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1" s="25" t="n">
         <v>45950.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -7462,24 +7403,24 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8"/>
@@ -7491,31 +7432,31 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26"/>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8"/>
@@ -7523,11 +7464,11 @@
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -7536,27 +7477,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -7570,34 +7511,34 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9"/>
@@ -7607,7 +7548,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -7621,10 +7562,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
@@ -7634,7 +7575,7 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -7659,7 +7600,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -7697,7 +7638,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -7735,7 +7676,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -8104,7 +8045,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -8113,16 +8054,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -8142,37 +8083,37 @@
   <sheetData>
     <row r="1" spans="5:19">
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1" s="25" t="n">
         <v>45950.9236111111095</v>
       </c>
       <c r="J1" s="25"/>
       <c r="O1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -8184,24 +8125,24 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="O2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="8"/>
@@ -8213,45 +8154,45 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26"/>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="S4" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -8260,27 +8201,27 @@
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="S5" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="7" spans="1:10">
       <c r="A7" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -8294,34 +8235,34 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9"/>
@@ -8331,7 +8272,7 @@
     <row r="10" spans="1:1" ht="7.95" customHeight="1"/>
     <row r="11" spans="1:10">
       <c r="A11" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -8345,10 +8286,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="11"/>
-      <c r="C12" s="30"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
@@ -8358,7 +8299,7 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="31"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -8383,7 +8324,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="22"/>
@@ -8421,7 +8362,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="22"/>
@@ -8459,7 +8400,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="22"/>
@@ -8828,7 +8769,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763127194" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -8837,16 +8778,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763127194" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763127194" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763127194" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/Assets/Planning/QA/Revenger_BTL.xlsx
+++ b/Assets/Planning/QA/Revenger_BTL.xlsx
@@ -5,7 +5,7 @@
   <fileSharing readOnlyRecommended="0" userName="autoa"/>
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="22050" windowHeight="9885" tabRatio="500"/>
+    <workbookView activeTab="3" xWindow="240" yWindow="60" windowWidth="22050" windowHeight="9885" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="1" r:id="rId4"/>
@@ -22,10 +22,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1763650637" val="1228" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1763650637" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1763650637" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1763650637"/>
+      <pm:revision xmlns:pm="smNativeData" day="1764256315" val="1228" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1764256315" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1764256315" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1764256315"/>
     </ext>
   </extLst>
 </workbook>
@@ -109,7 +109,7 @@
     <t>Issue No.</t>
   </si>
   <si>
-    <t>473a238 - 25</t>
+    <t>07bbd7c - 30</t>
   </si>
   <si>
     <t>TD</t>
@@ -163,22 +163,22 @@
     <t>Category</t>
   </si>
   <si>
-    <t>Design</t>
+    <t>Design, Script</t>
   </si>
   <si>
     <t>Charger</t>
   </si>
   <si>
-    <t>엄기영</t>
+    <t>이민기,엄기영</t>
   </si>
   <si>
     <t>Detail</t>
   </si>
   <si>
-    <t>외부 건물 기둥에 콜리전 누락</t>
+    <t>하수구 퍼즐 진입 카메라 바운더리 버그</t>
   </si>
   <si>
-    <t>건물 기둥에 히트박스가 존재하지 않음</t>
+    <t>하수구 퍼즐에 진입시 근처에 있는 세탁기 오브젝트가 사라지는 버그가 있음</t>
   </si>
   <si>
     <t>Replay</t>
@@ -187,13 +187,13 @@
     <t>Comment</t>
   </si>
   <si>
-    <t>기둥에 히트박스 추가 요청</t>
+    <t>카메라 바운더리를 수정하는 작업이 필요</t>
   </si>
   <si>
     <t>Steel shot</t>
   </si>
   <si>
-    <t>473a238 - 26</t>
+    <t>07bbd7c - 31</t>
   </si>
   <si>
     <t>Scripts</t>
@@ -202,25 +202,25 @@
     <t>이민기</t>
   </si>
   <si>
-    <t>(디버그) 노클립 이후 퍼즐 시퀀스 버그</t>
+    <t>식당 퍼즐 UI 나가기 불가</t>
   </si>
   <si>
-    <t>노클립사용 이후 퍼즐 이용시 하수구 퍼즐 시퀀스만 들어가지는 버그</t>
+    <t>식당 퍼즐 진행시 UI 창 나온 이후 상호작용포함 화면을 나갈 수도 없는 버그 발생</t>
   </si>
   <si>
-    <t>상호작용이 해당 퍼즐로 목표가 잡혀있는데 다른곳으로 강제 이동되어 생긴 문제 (급히 수정됨)</t>
+    <t>튜토리얼 Ui추가 이후 식당 Ui쪽에 문제가 있는거 같이 생각됨</t>
   </si>
   <si>
-    <t>473a238 - 27</t>
+    <t>07bbd7c - 32</t>
   </si>
   <si>
-    <t>갑자기 모든 경비원에게 발각 버그</t>
+    <t xml:space="preserve">게임오버 이후 Home에서의 튜토리얼 창 중복 및 스킵 불가 </t>
   </si>
   <si>
-    <t>뛰어다니면 가끔씩 모든 경비병에게 발각되는 버그가 있음</t>
+    <t>게임오버 이후 Home에서의 튜토리얼 창 중복으로 다시 출력되고 스킵이 안되어 게임 진행 불가</t>
   </si>
   <si>
-    <t>경비병에게 발각되는 기준을 확실히 알기가 어려워 원인 파악이 힘듬</t>
+    <t xml:space="preserve">게임 오버시 Home으로 돌아올때 튜토리얼 Ui는 생략하는 시스템 필요 </t>
   </si>
   <si>
     <t>473a238 - 28</t>
@@ -279,7 +279,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -294,7 +294,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -310,7 +310,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="180" lang="default"/>
             <pm:cs face="Times New Roman" sz="180" lang="default"/>
             <pm:ea face="SimSun" sz="180" lang="default"/>
@@ -327,7 +327,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -342,7 +342,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default"/>
             <pm:cs face="Times New Roman" sz="180" lang="default"/>
             <pm:ea face="SimSun" sz="180" lang="default"/>
@@ -358,7 +358,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
@@ -374,7 +374,7 @@
       <sz val="12"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="240" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="240" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="240" lang="default" weight="bold"/>
@@ -391,7 +391,7 @@
       <sz val="6"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="120" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="120" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="120" lang="default" weight="bold"/>
@@ -407,7 +407,7 @@
       <sz val="6"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" ulstyle="none" kern="1">
             <pm:latin face="맑은 고딕" sz="120" lang="default"/>
             <pm:cs face="Times New Roman" sz="120" lang="default"/>
             <pm:ea face="SimSun" sz="120" lang="default"/>
@@ -423,7 +423,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
@@ -438,7 +438,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default"/>
             <pm:cs face="Times New Roman" sz="160" lang="default"/>
             <pm:ea face="SimSun" sz="160" lang="default"/>
@@ -455,7 +455,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -473,7 +473,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -491,7 +491,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -509,7 +509,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -527,7 +527,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -545,7 +545,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -563,7 +563,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -581,7 +581,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -599,7 +599,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -617,7 +617,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -635,7 +635,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -653,7 +653,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -671,7 +671,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1763650637" fgClr="0000FF" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1764256315" fgClr="0000FF" ulstyle="single" kern="1">
             <pm:latin face="맑은 고딕" sz="220" lang="default"/>
             <pm:cs face="맑은 고딕" sz="220" lang="default"/>
             <pm:ea face="맑은 고딕" sz="220" lang="default"/>
@@ -694,7 +694,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1763650637" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1764256315" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -708,7 +708,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1763650637" type="1" fgLvl="100" fgClr="00D8D8D8" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1764256315" type="1" fgLvl="100" fgClr="00D8D8D8" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -719,7 +719,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1763650637" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1764256315" type="1" fgLvl="100" fgClr="00BFBFBF" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -757,7 +757,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1763650637" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1764256315" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -779,7 +779,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637"/>
+          <pm:border xmlns:pm="smNativeData" id="1764256315"/>
         </ext>
       </extLst>
     </border>
@@ -798,7 +798,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637"/>
+          <pm:border xmlns:pm="smNativeData" id="1764256315"/>
         </ext>
       </extLst>
     </border>
@@ -817,7 +817,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637">
+          <pm:border xmlns:pm="smNativeData" id="1764256315">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -841,7 +841,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637">
+          <pm:border xmlns:pm="smNativeData" id="1764256315">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -865,7 +865,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637">
+          <pm:border xmlns:pm="smNativeData" id="1764256315">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -889,7 +889,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637">
+          <pm:border xmlns:pm="smNativeData" id="1764256315">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
         </ext>
@@ -910,7 +910,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637">
+          <pm:border xmlns:pm="smNativeData" id="1764256315">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -932,7 +932,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637">
+          <pm:border xmlns:pm="smNativeData" id="1764256315">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
         </ext>
@@ -953,7 +953,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637">
+          <pm:border xmlns:pm="smNativeData" id="1764256315">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -975,7 +975,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637">
+          <pm:border xmlns:pm="smNativeData" id="1764256315">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -997,7 +997,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637">
+          <pm:border xmlns:pm="smNativeData" id="1764256315">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1019,7 +1019,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637">
+          <pm:border xmlns:pm="smNativeData" id="1764256315">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1042,7 +1042,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637">
+          <pm:border xmlns:pm="smNativeData" id="1764256315">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1064,7 +1064,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637">
+          <pm:border xmlns:pm="smNativeData" id="1764256315">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1087,7 +1087,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1763650637"/>
+          <pm:border xmlns:pm="smNativeData" id="1764256315"/>
         </ext>
       </extLst>
     </border>
@@ -1241,10 +1241,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1763650637" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1764256315" count="1">
         <pm:charStyle name="보통" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1763650637" count="2">
+      <pm:colors xmlns:pm="smNativeData" id="1764256315" count="2">
         <pm:color name="색: 24" rgb="D8D8D8"/>
         <pm:color name="색: 25" rgb="BFBFBF"/>
       </pm:colors>
@@ -1258,15 +1258,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>37465</xdr:rowOff>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>96520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>666115</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>64770</xdr:rowOff>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>99695</xdr:rowOff>
     </xdr:to>
     <xdr:pic macro="">
       <xdr:nvPicPr>
@@ -1275,7 +1275,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_TSwfaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAYAgAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAAAAAI4AAAAjAAAACQAAAPUA8gMAAAAAAiEAAIEpAAB3FwAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_O2ooaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAABlZj0iHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAWAAAAAAAAAG4BAQAkAAAACQAAAHoBxwMBAAAACSMAAFQpAABRFwAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1288,8 +1288,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="5365750"/>
-          <a:ext cx="6746875" cy="3814445"/>
+          <a:off x="635" y="5695315"/>
+          <a:ext cx="6718300" cy="3790315"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1314,6 +1314,118 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>175895</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>70485</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="smNativeData">
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_O2ooaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAXAAAAAAAAAJoCAQAlAAAACQAAAAwBuQMBAAAAMCUAAEUpAACmFgAAAAAAAA=="/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635" y="6045200"/>
+          <a:ext cx="6708775" cy="3681730"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>97790</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="smNativeData">
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_O2ooaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAoKCj/HgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAZAAAAAAAAAHMBAQAnAAAACQAAAAoD1gMBAAAACSgAAGMpAAD2FwAAAAAAAA=="/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635" y="6508115"/>
+          <a:ext cx="6727825" cy="3895090"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>241300</xdr:rowOff>
@@ -1331,7 +1443,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_TSwfaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAWAAAAAAAAAJEDDgAlAAAACQAAACgDawMPAAAA7SMAAOYoAADKGAAAAAAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_O2ooaRMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAWAAAAAAAAAJEDDgAlAAAACQAAACgDawMPAAAA7SMAAOYoAADKGAAAAAAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1621,7 +1733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="7.297521" customWidth="1" style="7"/>
@@ -1639,7 +1751,7 @@
       </c>
       <c r="G1" s="14">
         <f aca="1">TODAY()</f>
-        <v>45981</v>
+        <v>45989</v>
       </c>
       <c r="H1" s="14"/>
     </row>
@@ -1683,19 +1795,19 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="35" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" s="9">
         <f>'12'!C4</f>
-        <v>45981</v>
+        <v>45988</v>
       </c>
       <c r="C4" s="8" t="str">
         <f>'12'!C3</f>
-        <v>473a238 - 25</v>
+        <v>07bbd7c - 30</v>
       </c>
       <c r="D4" s="8" t="str">
         <f>'12'!C9</f>
-        <v>Design</v>
+        <v>Design, Script</v>
       </c>
       <c r="E4" s="8" t="str">
         <f>'12'!C5</f>
@@ -1703,7 +1815,7 @@
       </c>
       <c r="F4" s="12" t="str">
         <f>'12'!C12</f>
-        <v>외부 건물 기둥에 콜리전 누락</v>
+        <v>하수구 퍼즐 진입 카메라 바운더리 버그</v>
       </c>
       <c r="G4" s="8" t="str">
         <f>'12'!H4</f>
@@ -1711,20 +1823,20 @@
       </c>
       <c r="H4" s="8" t="str">
         <f>'12'!H9</f>
-        <v>엄기영</v>
+        <v>이민기,엄기영</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="36" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B5" s="9">
         <f>'13'!C4</f>
-        <v>45981</v>
+        <v>45988</v>
       </c>
       <c r="C5" s="8" t="str">
         <f>'13'!C3</f>
-        <v>473a238 - 26</v>
+        <v>07bbd7c - 31</v>
       </c>
       <c r="D5" s="8" t="str">
         <f>'13'!C9</f>
@@ -1736,7 +1848,7 @@
       </c>
       <c r="F5" s="12" t="str">
         <f>'13'!C12</f>
-        <v>(디버그) 노클립 이후 퍼즐 시퀀스 버그</v>
+        <v>식당 퍼즐 UI 나가기 불가</v>
       </c>
       <c r="G5" s="8" t="str">
         <f>'12'!H4</f>
@@ -1749,15 +1861,15 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="37" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B6" s="9">
         <f>'14'!C4</f>
-        <v>45981</v>
+        <v>45988</v>
       </c>
       <c r="C6" s="8" t="str">
         <f>'14'!C3</f>
-        <v>473a238 - 27</v>
+        <v>07bbd7c - 32</v>
       </c>
       <c r="D6" s="8" t="str">
         <f>'14'!C9</f>
@@ -1769,7 +1881,7 @@
       </c>
       <c r="F6" s="12" t="str">
         <f>'14'!C12</f>
-        <v>갑자기 모든 경비원에게 발각 버그</v>
+        <v>게임오버 이후 Home에서의 튜토리얼 창 중복 및 스킵 불가 </v>
       </c>
       <c r="G6" s="8" t="str">
         <f>'12'!H4</f>
@@ -1781,70 +1893,24 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="B7" s="9">
-        <f>'15'!C4</f>
-        <v>45981</v>
-      </c>
-      <c r="C7" s="8" t="str">
-        <f>'15'!C3</f>
-        <v>473a238 - 28</v>
-      </c>
-      <c r="D7" s="8" t="str">
-        <f>'15'!C9</f>
-        <v>Scripts</v>
-      </c>
-      <c r="E7" s="8" t="str">
-        <f>'15'!C5</f>
-        <v>Mid</v>
-      </c>
-      <c r="F7" s="12" t="str">
-        <f>'15'!C12</f>
-        <v>Dress/Guest 퍼즐 클리어후에도 다이얼 UI 접근 가능 </v>
-      </c>
-      <c r="G7" s="8" t="str">
-        <f>'12'!H4</f>
-        <v>김사윤</v>
-      </c>
-      <c r="H7" s="8" t="str">
-        <f>'15'!H9</f>
-        <v>이민기</v>
-      </c>
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="39" t="n">
-        <v>16</v>
-      </c>
-      <c r="B8" s="9">
-        <f>'16'!C4</f>
-        <v>45968</v>
-      </c>
-      <c r="C8" s="8" t="str">
-        <f>'16'!C3</f>
-        <v>473a238 - 29</v>
-      </c>
-      <c r="D8" s="8" t="str">
-        <f>'16'!C9</f>
-        <v>Scripts</v>
-      </c>
-      <c r="E8" s="8" t="str">
-        <f>'16'!C5</f>
-        <v>Mid</v>
-      </c>
-      <c r="F8" s="12" t="str">
-        <f>'16'!C12</f>
-        <v>식당 퍼즐 ui 일시정지 UI 꼬임</v>
-      </c>
-      <c r="G8" s="8" t="str">
-        <f>'12'!H4</f>
-        <v>김사윤</v>
-      </c>
-      <c r="H8" s="8" t="str">
-        <f>'16'!H9</f>
-        <v>이민기</v>
-      </c>
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="8"/>
@@ -2160,6 +2226,72 @@
         <v>0</v>
       </c>
     </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" s="9">
+        <f>'15'!C4</f>
+        <v>45981</v>
+      </c>
+      <c r="C31" s="8" t="str">
+        <f>'15'!C3</f>
+        <v>473a238 - 28</v>
+      </c>
+      <c r="D31" s="8" t="str">
+        <f>'15'!C9</f>
+        <v>Scripts</v>
+      </c>
+      <c r="E31" s="8" t="str">
+        <f>'15'!C5</f>
+        <v>Mid</v>
+      </c>
+      <c r="F31" s="12" t="str">
+        <f>'15'!C12</f>
+        <v>Dress/Guest 퍼즐 클리어후에도 다이얼 UI 접근 가능 </v>
+      </c>
+      <c r="G31" s="8" t="str">
+        <f>'12'!H4</f>
+        <v>김사윤</v>
+      </c>
+      <c r="H31" s="8" t="str">
+        <f>'15'!H9</f>
+        <v>이민기</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="39" t="n">
+        <v>16</v>
+      </c>
+      <c r="B32" s="9">
+        <f>'16'!C4</f>
+        <v>45968</v>
+      </c>
+      <c r="C32" s="8" t="str">
+        <f>'16'!C3</f>
+        <v>473a238 - 29</v>
+      </c>
+      <c r="D32" s="8" t="str">
+        <f>'16'!C9</f>
+        <v>Scripts</v>
+      </c>
+      <c r="E32" s="8" t="str">
+        <f>'16'!C5</f>
+        <v>Mid</v>
+      </c>
+      <c r="F32" s="12" t="str">
+        <f>'16'!C12</f>
+        <v>식당 퍼즐 ui 일시정지 UI 꼬임</v>
+      </c>
+      <c r="G32" s="8" t="str">
+        <f>'12'!H4</f>
+        <v>김사윤</v>
+      </c>
+      <c r="H32" s="8" t="str">
+        <f>'16'!H9</f>
+        <v>이민기</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="G1:H1"/>
@@ -2169,8 +2301,6 @@
     <hyperlink ref="A4" location="'12'!A1"/>
     <hyperlink ref="A5" location="'13'!A1"/>
     <hyperlink ref="A6" location="'14'!A1"/>
-    <hyperlink ref="A7" location="'15'!A1"/>
-    <hyperlink ref="A8" location="'16'!A1"/>
     <hyperlink ref="A13" location="'9-2'!A1"/>
     <hyperlink ref="A14" location="'10-1'!A1"/>
     <hyperlink ref="A15" location="'10-2'!A1"/>
@@ -2179,11 +2309,13 @@
     <hyperlink ref="A28" location="'18'!A1"/>
     <hyperlink ref="A29" location="'19'!A1"/>
     <hyperlink ref="A30" location="'20'!A1"/>
+    <hyperlink ref="A31" location="'15'!A1"/>
+    <hyperlink ref="A32" location="'16'!A1"/>
   </hyperlinks>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1764256315" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2192,16 +2324,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1764256315" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -2907,7 +3039,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1764256315" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2916,17 +3048,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1764256315" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -3040,7 +3172,7 @@
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45981</v>
+        <v>45988</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
@@ -3115,7 +3247,7 @@
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -3646,7 +3778,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1764256315" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -3655,17 +3787,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1764256315" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -3779,7 +3911,7 @@
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45981</v>
+        <v>45988</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
@@ -3845,7 +3977,7 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -3854,7 +3986,7 @@
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -4385,7 +4517,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1764256315" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -4394,16 +4526,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1764256315" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -4517,7 +4650,7 @@
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="26" t="n">
-        <v>45981</v>
+        <v>45988</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="28"/>
@@ -4583,7 +4716,7 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="9" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -4592,7 +4725,7 @@
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -5123,7 +5256,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1764256315" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -5132,16 +5265,17 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1764256315" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -5861,7 +5995,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1764256315" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -5870,16 +6004,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1764256315" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -6599,7 +6733,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1764256315" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -6608,16 +6742,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1764256315" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -7323,7 +7457,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1764256315" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -7332,16 +7466,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1764256315" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -8045,7 +8179,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1764256315" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -8054,16 +8188,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1764256315" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -8769,7 +8903,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1763650637" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1764256315" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -8778,16 +8912,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1763650637" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1763650637" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1764256315" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1764256315" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1763650637" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1764256315" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
